--- a/output.xlsx
+++ b/output.xlsx
@@ -11074,7 +11074,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>33/42</t>
+          <t>33/43</t>
         </is>
       </c>
     </row>
@@ -11091,38 +11091,38 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>.453</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>.747</t>
+          <t>.745</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F173" t="n">
-        <v>389</v>
+        <v>434</v>
       </c>
       <c r="G173" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="H173" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I173" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J173" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>31/44</t>
+          <t>34/43</t>
         </is>
       </c>
     </row>
@@ -11139,25 +11139,25 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.504</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>.840</t>
+          <t>.837</t>
         </is>
       </c>
       <c r="E174" t="n">
         <v>63</v>
       </c>
       <c r="F174" t="n">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="G174" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H174" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I174" t="n">
         <v>36</v>
@@ -11166,11 +11166,11 @@
         <v>15</v>
       </c>
       <c r="K174" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>31/42</t>
+          <t>32/42</t>
         </is>
       </c>
     </row>
@@ -11187,38 +11187,38 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>.481</t>
+          <t>.493</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>.825</t>
+          <t>.835</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F175" t="n">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="G175" t="n">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H175" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I175" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J175" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>28/42</t>
+          <t>30/39</t>
         </is>
       </c>
     </row>
@@ -11235,38 +11235,38 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>.873</t>
+          <t>.864</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F176" t="n">
-        <v>416</v>
+        <v>536</v>
       </c>
       <c r="G176" t="n">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="H176" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="I176" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J176" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K176" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>27/40</t>
+          <t>33/37</t>
         </is>
       </c>
     </row>
@@ -11283,38 +11283,38 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>.475</t>
+          <t>.480</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>.767</t>
+          <t>.725</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F177" t="n">
-        <v>310</v>
+        <v>363</v>
       </c>
       <c r="G177" t="n">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="H177" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I177" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J177" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K177" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>25/36</t>
+          <t>28/35</t>
         </is>
       </c>
     </row>
@@ -11331,38 +11331,38 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>.420</t>
+          <t>.431</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>.768</t>
+          <t>.770</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F178" t="n">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="G178" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H178" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="I178" t="n">
         <v>24</v>
       </c>
       <c r="J178" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K178" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>27/41</t>
+          <t>30/40</t>
         </is>
       </c>
     </row>
@@ -11379,38 +11379,38 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>.518</t>
+          <t>.509</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>.755</t>
+          <t>.741</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F179" t="n">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="G179" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H179" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I179" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J179" t="n">
         <v>16</v>
       </c>
       <c r="K179" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>35/47</t>
+          <t>37/47</t>
         </is>
       </c>
     </row>
@@ -11427,38 +11427,38 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>.455</t>
+          <t>.460</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>.797</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E180" t="n">
+        <v>84</v>
+      </c>
+      <c r="F180" t="n">
+        <v>604</v>
+      </c>
+      <c r="G180" t="n">
+        <v>157</v>
+      </c>
+      <c r="H180" t="n">
+        <v>133</v>
+      </c>
+      <c r="I180" t="n">
+        <v>40</v>
+      </c>
+      <c r="J180" t="n">
+        <v>20</v>
+      </c>
+      <c r="K180" t="n">
         <v>64</v>
       </c>
-      <c r="F180" t="n">
-        <v>475</v>
-      </c>
-      <c r="G180" t="n">
-        <v>120</v>
-      </c>
-      <c r="H180" t="n">
-        <v>110</v>
-      </c>
-      <c r="I180" t="n">
-        <v>36</v>
-      </c>
-      <c r="J180" t="n">
-        <v>16</v>
-      </c>
-      <c r="K180" t="n">
-        <v>53</v>
-      </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>30/41</t>
+          <t>35/41</t>
         </is>
       </c>
     </row>
@@ -11480,20 +11480,20 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>.674</t>
+          <t>.688</t>
         </is>
       </c>
       <c r="E181" t="n">
         <v>25</v>
       </c>
       <c r="F181" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G181" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H181" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I181" t="n">
         <v>22</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>0/43</t>
+          <t>0/42</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>0/43</t>
+          <t>0/45</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>0/39</t>
+          <t>0/33</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11091,25 +11091,25 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.441</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>.745</t>
+          <t>.757</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F173" t="n">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="G173" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H173" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I173" t="n">
         <v>43</v>
@@ -11118,11 +11118,11 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>34/43</t>
+          <t>36/45</t>
         </is>
       </c>
     </row>
@@ -11187,38 +11187,38 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>.493</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>.835</t>
+          <t>.821</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F175" t="n">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="G175" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H175" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I175" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J175" t="n">
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>30/39</t>
+          <t>34/43</t>
         </is>
       </c>
     </row>
@@ -11240,33 +11240,33 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>.864</t>
+          <t>.863</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F176" t="n">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="G176" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H176" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I176" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J176" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>33/37</t>
+          <t>36/40</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>.480</t>
+          <t>.479</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11298,10 +11298,10 @@
         <v>363</v>
       </c>
       <c r="G177" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H177" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I177" t="n">
         <v>30</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>28/35</t>
+          <t>29/36</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>30/40</t>
+          <t>31/41</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>.509</t>
+          <t>.510</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11391,13 +11391,13 @@
         <v>55</v>
       </c>
       <c r="F179" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G179" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H179" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I179" t="n">
         <v>33</v>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>38/48</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>.460</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11436,16 +11436,16 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F180" t="n">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="G180" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H180" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I180" t="n">
         <v>40</v>
@@ -11454,11 +11454,11 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>35/41</t>
+          <t>37/43</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11202,7 +11202,7 @@
         <v>545</v>
       </c>
       <c r="G175" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H175" t="n">
         <v>98</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>34/43</t>
+          <t>34/44</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>0/42</t>
+          <t>0/46</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>.508</t>
+          <t>.520</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11052,29 +11052,29 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F172" t="n">
-        <v>415</v>
+        <v>597</v>
       </c>
       <c r="G172" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="H172" t="n">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="I172" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="J172" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K172" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>33/43</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11091,38 +11091,38 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>.441</t>
+          <t>.442</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>.757</t>
+          <t>.762</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F173" t="n">
-        <v>452</v>
+        <v>582</v>
       </c>
       <c r="G173" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="H173" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="I173" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J173" t="n">
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>36/45</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -11139,38 +11139,38 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>.504</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>.837</t>
+          <t>.825</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F174" t="n">
-        <v>502</v>
+        <v>647</v>
       </c>
       <c r="G174" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="H174" t="n">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I174" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J174" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K174" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>32/42</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -11187,38 +11187,38 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>.491</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>.821</t>
+          <t>.801</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F175" t="n">
-        <v>545</v>
+        <v>678</v>
       </c>
       <c r="G175" t="n">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="H175" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="I175" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J175" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K175" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>34/44</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.471</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11244,29 +11244,29 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F176" t="n">
-        <v>561</v>
+        <v>623</v>
       </c>
       <c r="G176" t="n">
+        <v>186</v>
+      </c>
+      <c r="H176" t="n">
         <v>159</v>
       </c>
-      <c r="H176" t="n">
-        <v>152</v>
-      </c>
       <c r="I176" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J176" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K176" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>36/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11283,38 +11283,38 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>.479</t>
+          <t>.474</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>.725</t>
+          <t>.738</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F177" t="n">
-        <v>363</v>
+        <v>463</v>
       </c>
       <c r="G177" t="n">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="H177" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="I177" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J177" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K177" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>29/36</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -11331,38 +11331,38 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>.431</t>
+          <t>.445</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>.770</t>
+          <t>.729</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F178" t="n">
-        <v>413</v>
+        <v>574</v>
       </c>
       <c r="G178" t="n">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="H178" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I178" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J178" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K178" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>31/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11379,38 +11379,38 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>.510</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>.741</t>
+          <t>.734</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F179" t="n">
-        <v>590</v>
+        <v>695</v>
       </c>
       <c r="G179" t="n">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="H179" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I179" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J179" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K179" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>38/48</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -11427,38 +11427,38 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.456</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.798</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F180" t="n">
-        <v>621</v>
+        <v>662</v>
       </c>
       <c r="G180" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="H180" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="I180" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J180" t="n">
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>37/43</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11475,38 +11475,38 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>.511</t>
+          <t>.506</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>.688</t>
+          <t>.683</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F181" t="n">
-        <v>244</v>
+        <v>315</v>
       </c>
       <c r="G181" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="H181" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I181" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J181" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K181" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>30/30</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/44</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>0/45</t>
+          <t>0/34</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>0/42</t>
+          <t>0/38</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>0/24</t>
+          <t>0/20</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11043,7 +11043,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>.520</t>
+          <t>.519</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -11058,13 +11058,13 @@
         <v>597</v>
       </c>
       <c r="G172" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H172" t="n">
         <v>124</v>
       </c>
       <c r="I172" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J172" t="n">
         <v>45</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -11091,25 +11091,25 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>.442</t>
+          <t>.439</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>.762</t>
+          <t>.765</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F173" t="n">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="G173" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H173" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I173" t="n">
         <v>45</v>
@@ -11118,11 +11118,11 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -11139,28 +11139,28 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.478</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>.825</t>
+          <t>.820</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F174" t="n">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="G174" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H174" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I174" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J174" t="n">
         <v>24</v>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -11192,33 +11192,33 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>.801</t>
+          <t>.804</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F175" t="n">
-        <v>678</v>
+        <v>704</v>
       </c>
       <c r="G175" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="H175" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I175" t="n">
         <v>25</v>
       </c>
       <c r="J175" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K175" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -11235,38 +11235,38 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>.471</t>
+          <t>.474</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>.863</t>
+          <t>.861</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F176" t="n">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="G176" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H176" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I176" t="n">
         <v>49</v>
       </c>
       <c r="J176" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K176" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11283,38 +11283,38 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>.474</t>
+          <t>.473</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>.738</t>
+          <t>.748</t>
         </is>
       </c>
       <c r="E177" t="n">
         <v>26</v>
       </c>
       <c r="F177" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="G177" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H177" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I177" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J177" t="n">
         <v>38</v>
       </c>
       <c r="K177" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>34/34</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>.445</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11343,26 +11343,26 @@
         <v>59</v>
       </c>
       <c r="F178" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="G178" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H178" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I178" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J178" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K178" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -11379,22 +11379,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>.734</t>
+          <t>.729</t>
         </is>
       </c>
       <c r="E179" t="n">
         <v>71</v>
       </c>
       <c r="F179" t="n">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="G179" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H179" t="n">
         <v>126</v>
@@ -11403,14 +11403,14 @@
         <v>42</v>
       </c>
       <c r="J179" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K179" t="n">
         <v>64</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -11427,38 +11427,38 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>.456</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>.798</t>
+          <t>.779</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F180" t="n">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="G180" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H180" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I180" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J180" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K180" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -11475,38 +11475,38 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>.506</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>.683</t>
+          <t>.677</t>
         </is>
       </c>
       <c r="E181" t="n">
         <v>36</v>
       </c>
       <c r="F181" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="G181" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H181" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I181" t="n">
         <v>27</v>
       </c>
       <c r="J181" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K181" t="n">
         <v>42</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>0/42</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/42</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11051,26 +11051,40 @@
           <t>.787</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>48</v>
-      </c>
-      <c r="F172" t="n">
-        <v>597</v>
-      </c>
-      <c r="G172" t="n">
-        <v>220</v>
-      </c>
-      <c r="H172" t="n">
-        <v>124</v>
-      </c>
-      <c r="I172" t="n">
-        <v>50</v>
-      </c>
-      <c r="J172" t="n">
-        <v>45</v>
-      </c>
-      <c r="K172" t="n">
-        <v>50</v>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -11099,26 +11113,40 @@
           <t>.765</t>
         </is>
       </c>
-      <c r="E173" t="n">
-        <v>63</v>
-      </c>
-      <c r="F173" t="n">
-        <v>589</v>
-      </c>
-      <c r="G173" t="n">
-        <v>218</v>
-      </c>
-      <c r="H173" t="n">
-        <v>157</v>
-      </c>
-      <c r="I173" t="n">
-        <v>45</v>
-      </c>
-      <c r="J173" t="n">
-        <v>20</v>
-      </c>
-      <c r="K173" t="n">
-        <v>90</v>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -11147,26 +11175,40 @@
           <t>.820</t>
         </is>
       </c>
-      <c r="E174" t="n">
-        <v>87</v>
-      </c>
-      <c r="F174" t="n">
-        <v>657</v>
-      </c>
-      <c r="G174" t="n">
-        <v>194</v>
-      </c>
-      <c r="H174" t="n">
-        <v>155</v>
-      </c>
-      <c r="I174" t="n">
-        <v>50</v>
-      </c>
-      <c r="J174" t="n">
-        <v>24</v>
-      </c>
-      <c r="K174" t="n">
-        <v>66</v>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -11195,26 +11237,40 @@
           <t>.804</t>
         </is>
       </c>
-      <c r="E175" t="n">
-        <v>79</v>
-      </c>
-      <c r="F175" t="n">
-        <v>704</v>
-      </c>
-      <c r="G175" t="n">
-        <v>262</v>
-      </c>
-      <c r="H175" t="n">
-        <v>143</v>
-      </c>
-      <c r="I175" t="n">
-        <v>25</v>
-      </c>
-      <c r="J175" t="n">
-        <v>26</v>
-      </c>
-      <c r="K175" t="n">
-        <v>76</v>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -11235,7 +11291,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>.474</t>
+          <t>.475</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11243,26 +11299,40 @@
           <t>.861</t>
         </is>
       </c>
-      <c r="E176" t="n">
-        <v>74</v>
-      </c>
-      <c r="F176" t="n">
-        <v>643</v>
-      </c>
-      <c r="G176" t="n">
-        <v>187</v>
-      </c>
-      <c r="H176" t="n">
-        <v>163</v>
-      </c>
-      <c r="I176" t="n">
-        <v>49</v>
-      </c>
-      <c r="J176" t="n">
-        <v>19</v>
-      </c>
-      <c r="K176" t="n">
-        <v>86</v>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -11291,26 +11361,40 @@
           <t>.748</t>
         </is>
       </c>
-      <c r="E177" t="n">
-        <v>26</v>
-      </c>
-      <c r="F177" t="n">
-        <v>474</v>
-      </c>
-      <c r="G177" t="n">
-        <v>243</v>
-      </c>
-      <c r="H177" t="n">
-        <v>134</v>
-      </c>
-      <c r="I177" t="n">
-        <v>37</v>
-      </c>
-      <c r="J177" t="n">
-        <v>38</v>
-      </c>
-      <c r="K177" t="n">
-        <v>75</v>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -11339,26 +11423,40 @@
           <t>.729</t>
         </is>
       </c>
-      <c r="E178" t="n">
-        <v>59</v>
-      </c>
-      <c r="F178" t="n">
-        <v>580</v>
-      </c>
-      <c r="G178" t="n">
-        <v>242</v>
-      </c>
-      <c r="H178" t="n">
-        <v>140</v>
-      </c>
-      <c r="I178" t="n">
-        <v>32</v>
-      </c>
-      <c r="J178" t="n">
-        <v>35</v>
-      </c>
-      <c r="K178" t="n">
-        <v>91</v>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -11387,26 +11485,40 @@
           <t>.729</t>
         </is>
       </c>
-      <c r="E179" t="n">
-        <v>71</v>
-      </c>
-      <c r="F179" t="n">
-        <v>704</v>
-      </c>
-      <c r="G179" t="n">
-        <v>267</v>
-      </c>
-      <c r="H179" t="n">
-        <v>126</v>
-      </c>
-      <c r="I179" t="n">
-        <v>42</v>
-      </c>
-      <c r="J179" t="n">
-        <v>20</v>
-      </c>
-      <c r="K179" t="n">
-        <v>64</v>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -11435,26 +11547,40 @@
           <t>.779</t>
         </is>
       </c>
-      <c r="E180" t="n">
-        <v>97</v>
-      </c>
-      <c r="F180" t="n">
-        <v>680</v>
-      </c>
-      <c r="G180" t="n">
-        <v>181</v>
-      </c>
-      <c r="H180" t="n">
-        <v>157</v>
-      </c>
-      <c r="I180" t="n">
-        <v>48</v>
-      </c>
-      <c r="J180" t="n">
-        <v>21</v>
-      </c>
-      <c r="K180" t="n">
-        <v>72</v>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -11483,26 +11609,40 @@
           <t>.677</t>
         </is>
       </c>
-      <c r="E181" t="n">
-        <v>36</v>
-      </c>
-      <c r="F181" t="n">
-        <v>324</v>
-      </c>
-      <c r="G181" t="n">
-        <v>109</v>
-      </c>
-      <c r="H181" t="n">
-        <v>78</v>
-      </c>
-      <c r="I181" t="n">
-        <v>27</v>
-      </c>
-      <c r="J181" t="n">
-        <v>13</v>
-      </c>
-      <c r="K181" t="n">
-        <v>42</v>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -11521,18 +11661,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>.278</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>4</v>
+      </c>
+      <c r="F182" t="n">
+        <v>18</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>9</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>2</v>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>0/32</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11547,18 +11709,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>.476</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>24</v>
+      </c>
+      <c r="G183" t="n">
+        <v>12</v>
+      </c>
+      <c r="H183" t="n">
+        <v>10</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" t="n">
+        <v>2</v>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>0/46</t>
+          <t>1/44</t>
         </is>
       </c>
     </row>
@@ -11573,18 +11757,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>.176</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" t="n">
+        <v>10</v>
+      </c>
+      <c r="G184" t="n">
+        <v>7</v>
+      </c>
+      <c r="H184" t="n">
+        <v>5</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="n">
+        <v>3</v>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>0/44</t>
+          <t>2/44</t>
         </is>
       </c>
     </row>
@@ -11599,18 +11805,36 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>.667</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="E185" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" t="n">
+        <v>14</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="n">
+        <v>6</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>0/38</t>
+          <t>0/44</t>
         </is>
       </c>
     </row>
@@ -11625,18 +11849,36 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>.667</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>4</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>0/42</t>
+          <t>0/34</t>
         </is>
       </c>
     </row>
@@ -11651,18 +11893,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>.500</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>.889</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>5</v>
+      </c>
+      <c r="F187" t="n">
+        <v>47</v>
+      </c>
+      <c r="G187" t="n">
+        <v>19</v>
+      </c>
+      <c r="H187" t="n">
+        <v>16</v>
+      </c>
+      <c r="I187" t="n">
+        <v>5</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="n">
+        <v>6</v>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>3/37</t>
         </is>
       </c>
     </row>
@@ -11677,18 +11941,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>.404</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>.500</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>10</v>
+      </c>
+      <c r="F188" t="n">
+        <v>53</v>
+      </c>
+      <c r="G188" t="n">
+        <v>15</v>
+      </c>
+      <c r="H188" t="n">
+        <v>19</v>
+      </c>
+      <c r="I188" t="n">
+        <v>7</v>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="n">
+        <v>4</v>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>0/33</t>
+          <t>2/36</t>
         </is>
       </c>
     </row>
@@ -11703,18 +11989,36 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>.556</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="E189" t="n">
+        <v>4</v>
+      </c>
+      <c r="F189" t="n">
+        <v>14</v>
+      </c>
+      <c r="G189" t="n">
+        <v>5</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>0/42</t>
+          <t>3/35</t>
         </is>
       </c>
     </row>
@@ -11729,18 +12033,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>.389</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>.714</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>19</v>
+      </c>
+      <c r="G190" t="n">
+        <v>11</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>3</v>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>0/20</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11755,18 +12081,40 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>.629</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>.750</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" t="n">
+        <v>54</v>
+      </c>
+      <c r="G191" t="n">
+        <v>25</v>
+      </c>
+      <c r="H191" t="n">
+        <v>6</v>
+      </c>
+      <c r="I191" t="n">
+        <v>3</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>10</v>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>0/36</t>
+          <t>2/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.476</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.909</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G183" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H183" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>1/44</t>
+          <t>2/45</t>
         </is>
       </c>
     </row>
@@ -11807,34 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.667</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>.533</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>.500</t>
+        </is>
+      </c>
       <c r="E185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F185" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H185" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I185" t="n">
         <v>1</v>
       </c>
       <c r="J185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>0/44</t>
+          <t>2/46</t>
         </is>
       </c>
     </row>
@@ -11851,34 +11855,34 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.667</t>
+          <t>.333</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" t="n">
         <v>1</v>
       </c>
-      <c r="H186" t="n">
-        <v>0</v>
-      </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>0/34</t>
+          <t>1/35</t>
         </is>
       </c>
     </row>
@@ -11895,38 +11899,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.574</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.889</t>
+          <t>.862</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F187" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="G187" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H187" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I187" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J187" t="n">
         <v>1</v>
       </c>
       <c r="K187" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>3/37</t>
+          <t>6/40</t>
         </is>
       </c>
     </row>
@@ -11943,25 +11947,25 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.404</t>
+          <t>.413</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G188" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H188" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I188" t="n">
         <v>7</v>
@@ -11974,7 +11978,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2/36</t>
+          <t>3/37</t>
         </is>
       </c>
     </row>
@@ -11991,21 +11995,25 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.556</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>.583</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>.500</t>
+        </is>
+      </c>
       <c r="E189" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F189" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G189" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I189" t="n">
         <v>1</v>
@@ -12014,7 +12022,7 @@
         <v>1</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -12035,34 +12043,34 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.389</t>
+          <t>.375</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.714</t>
+          <t>.778</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G190" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H190" t="n">
         <v>2</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K190" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11694,7 +11694,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.444</t>
+          <t>.419</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11720,29 +11720,29 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G183" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H183" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J183" t="n">
         <v>3</v>
       </c>
       <c r="K183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2/45</t>
+          <t>3/46</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.533</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11822,10 +11822,10 @@
         <v>20</v>
       </c>
       <c r="G185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H185" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I185" t="n">
         <v>1</v>
@@ -11834,11 +11834,11 @@
         <v>2</v>
       </c>
       <c r="K185" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2/46</t>
+          <t>3/47</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>1/35</t>
+          <t>2/36</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.574</t>
+          <t>.585</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11908,19 +11908,19 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F187" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G187" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H187" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J187" t="n">
         <v>1</v>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>6/40</t>
+          <t>7/41</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>3/37</t>
+          <t>4/40</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.583</t>
+          <t>.519</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12013,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I189" t="n">
         <v>1</v>
@@ -12022,11 +12022,11 @@
         <v>1</v>
       </c>
       <c r="K189" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>3/35</t>
+          <t>4/36</t>
         </is>
       </c>
     </row>
@@ -12043,22 +12043,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.375</t>
+          <t>.419</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.778</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G190" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H190" t="n">
         <v>2</v>
@@ -12070,11 +12070,11 @@
         <v>2</v>
       </c>
       <c r="K190" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>2/32</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.821</t>
         </is>
       </c>
       <c r="E182" t="n">
+        <v>10</v>
+      </c>
+      <c r="F182" t="n">
+        <v>103</v>
+      </c>
+      <c r="G182" t="n">
+        <v>40</v>
+      </c>
+      <c r="H182" t="n">
+        <v>21</v>
+      </c>
+      <c r="I182" t="n">
         <v>4</v>
       </c>
-      <c r="F182" t="n">
-        <v>18</v>
-      </c>
-      <c r="G182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H182" t="n">
-        <v>9</v>
-      </c>
-      <c r="I182" t="n">
-        <v>1</v>
-      </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K182" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.419</t>
+          <t>.531</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.909</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="G183" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="H183" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I183" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J183" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K183" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>3/46</t>
+          <t>8/46</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.176</t>
+          <t>.402</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.773</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F184" t="n">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="G184" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H184" t="n">
+        <v>16</v>
+      </c>
+      <c r="I184" t="n">
+        <v>9</v>
+      </c>
+      <c r="J184" t="n">
         <v>5</v>
       </c>
-      <c r="I184" t="n">
-        <v>2</v>
-      </c>
-      <c r="J184" t="n">
-        <v>1</v>
-      </c>
       <c r="K184" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2/44</t>
+          <t>3/38</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.434</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.739</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F185" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="G185" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H185" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J185" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K185" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>3/47</t>
+          <t>9/48</t>
         </is>
       </c>
     </row>
@@ -11855,34 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.333</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>.427</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>.810</t>
+        </is>
+      </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F186" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K186" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2/36</t>
+          <t>8/38</t>
         </is>
       </c>
     </row>
@@ -11899,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.585</t>
+          <t>.505</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.862</t>
+          <t>.881</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F187" t="n">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="G187" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H187" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K187" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>7/41</t>
+          <t>10/42</t>
         </is>
       </c>
     </row>
@@ -11947,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.413</t>
+          <t>.450</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.929</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F188" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="G188" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H188" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I188" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J188" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K188" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>4/40</t>
+          <t>9/40</t>
         </is>
       </c>
     </row>
@@ -11995,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.519</t>
+          <t>.452</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F189" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G189" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H189" t="n">
+        <v>24</v>
+      </c>
+      <c r="I189" t="n">
+        <v>5</v>
+      </c>
+      <c r="J189" t="n">
         <v>4</v>
       </c>
-      <c r="I189" t="n">
-        <v>1</v>
-      </c>
-      <c r="J189" t="n">
-        <v>1</v>
-      </c>
       <c r="K189" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>4/36</t>
+          <t>8/35</t>
         </is>
       </c>
     </row>
@@ -12043,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.419</t>
+          <t>.478</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F190" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="G190" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H190" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J190" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12091,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.629</t>
+          <t>.575</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.727</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F191" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G191" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="H191" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J191" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K191" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2/36</t>
+          <t>4/32</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,7 +11663,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.493</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11678,7 +11678,7 @@
         <v>103</v>
       </c>
       <c r="G182" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H182" t="n">
         <v>21</v>
@@ -11690,11 +11690,11 @@
         <v>3</v>
       </c>
       <c r="K182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>11/37</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.531</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F183" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="G183" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H183" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K183" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>8/46</t>
+          <t>8/42</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.402</t>
+          <t>.419</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.773</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F184" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="G184" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H184" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I184" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>3/38</t>
+          <t>9/41</t>
         </is>
       </c>
     </row>
@@ -11807,25 +11807,25 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.434</t>
+          <t>.456</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.739</t>
+          <t>.741</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F185" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="G185" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H185" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I185" t="n">
         <v>8</v>
@@ -11834,11 +11834,11 @@
         <v>7</v>
       </c>
       <c r="K185" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>9/48</t>
+          <t>9/47</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.427</t>
+          <t>.436</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11867,26 +11867,26 @@
         <v>8</v>
       </c>
       <c r="F186" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G186" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H186" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I186" t="n">
         <v>9</v>
       </c>
       <c r="J186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K186" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>8/38</t>
+          <t>9/41</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.505</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11912,16 +11912,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F187" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G187" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H187" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I187" t="n">
         <v>9</v>
@@ -11930,11 +11930,11 @@
         <v>2</v>
       </c>
       <c r="K187" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>10/42</t>
+          <t>11/44</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.450</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.929</t>
+          <t>.895</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F188" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="G188" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H188" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I188" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J188" t="n">
         <v>9</v>
       </c>
       <c r="K188" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>9/40</t>
+          <t>9/37</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.452</t>
+          <t>.468</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.769</t>
         </is>
       </c>
       <c r="E189" t="n">
         <v>11</v>
       </c>
       <c r="F189" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G189" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H189" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J189" t="n">
         <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>8/35</t>
+          <t>11/42</t>
         </is>
       </c>
     </row>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.478</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.773</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F190" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="G190" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H190" t="n">
         <v>20</v>
@@ -12074,11 +12074,11 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.575</t>
+          <t>.548</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.727</t>
+          <t>.744</t>
         </is>
       </c>
       <c r="E191" t="n">
         <v>5</v>
       </c>
       <c r="F191" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G191" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H191" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I191" t="n">
         <v>14</v>
       </c>
       <c r="J191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K191" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>4/32</t>
+          <t>8/35</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11711,34 +11711,34 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.491</t>
+          <t>.485</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.886</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F183" t="n">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="G183" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H183" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I183" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J183" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K183" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -11759,34 +11759,34 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.419</t>
+          <t>.397</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.791</t>
         </is>
       </c>
       <c r="E184" t="n">
+        <v>20</v>
+      </c>
+      <c r="F184" t="n">
+        <v>170</v>
+      </c>
+      <c r="G184" t="n">
+        <v>61</v>
+      </c>
+      <c r="H184" t="n">
+        <v>26</v>
+      </c>
+      <c r="I184" t="n">
         <v>17</v>
-      </c>
-      <c r="F184" t="n">
-        <v>145</v>
-      </c>
-      <c r="G184" t="n">
-        <v>53</v>
-      </c>
-      <c r="H184" t="n">
-        <v>20</v>
-      </c>
-      <c r="I184" t="n">
-        <v>14</v>
       </c>
       <c r="J184" t="n">
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -11807,34 +11807,34 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.456</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.741</t>
+          <t>.677</t>
         </is>
       </c>
       <c r="E185" t="n">
         <v>13</v>
       </c>
       <c r="F185" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G185" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H185" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I185" t="n">
         <v>8</v>
       </c>
       <c r="J185" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K185" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -11855,22 +11855,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.436</t>
+          <t>.454</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.810</t>
+          <t>.818</t>
         </is>
       </c>
       <c r="E186" t="n">
         <v>8</v>
       </c>
       <c r="F186" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G186" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H186" t="n">
         <v>48</v>
@@ -11879,7 +11879,7 @@
         <v>9</v>
       </c>
       <c r="J186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K186" t="n">
         <v>16</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.491</t>
+          <t>.475</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11915,13 +11915,13 @@
         <v>20</v>
       </c>
       <c r="F187" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G187" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H187" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I187" t="n">
         <v>9</v>
@@ -11930,7 +11930,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -11951,34 +11951,34 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.460</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.895</t>
+          <t>.913</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F188" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G188" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H188" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I188" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J188" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K188" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.468</t>
+          <t>.477</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12011,10 +12011,10 @@
         <v>11</v>
       </c>
       <c r="F189" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G189" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H189" t="n">
         <v>25</v>
@@ -12023,7 +12023,7 @@
         <v>6</v>
       </c>
       <c r="J189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K189" t="n">
         <v>9</v>
@@ -12047,34 +12047,34 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.466</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.773</t>
+          <t>.769</t>
         </is>
       </c>
       <c r="E190" t="n">
+        <v>12</v>
+      </c>
+      <c r="F190" t="n">
+        <v>128</v>
+      </c>
+      <c r="G190" t="n">
+        <v>47</v>
+      </c>
+      <c r="H190" t="n">
+        <v>23</v>
+      </c>
+      <c r="I190" t="n">
         <v>10</v>
-      </c>
-      <c r="F190" t="n">
-        <v>105</v>
-      </c>
-      <c r="G190" t="n">
-        <v>42</v>
-      </c>
-      <c r="H190" t="n">
-        <v>20</v>
-      </c>
-      <c r="I190" t="n">
-        <v>9</v>
       </c>
       <c r="J190" t="n">
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>74</v>
       </c>
       <c r="H191" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I191" t="n">
         <v>14</v>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11711,25 +11711,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.485</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.886</t>
+          <t>.865</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>12</v>
       </c>
       <c r="F183" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G183" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H183" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I183" t="n">
         <v>14</v>
@@ -11738,11 +11738,11 @@
         <v>12</v>
       </c>
       <c r="K183" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>8/42</t>
+          <t>12/46</t>
         </is>
       </c>
     </row>
@@ -11759,25 +11759,25 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.397</t>
+          <t>.412</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.791</t>
+          <t>.795</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F184" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="G184" t="n">
         <v>61</v>
       </c>
       <c r="H184" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I184" t="n">
         <v>17</v>
@@ -11786,11 +11786,11 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>9/41</t>
+          <t>12/44</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>9/47</t>
+          <t>10/48</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>9/41</t>
+          <t>10/42</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.475</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11915,16 +11915,16 @@
         <v>20</v>
       </c>
       <c r="F187" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G187" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H187" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I187" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J187" t="n">
         <v>2</v>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>11/44</t>
+          <t>13/46</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.460</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11960,29 +11960,29 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F188" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G188" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H188" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I188" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J188" t="n">
         <v>11</v>
       </c>
       <c r="K188" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>9/37</t>
+          <t>12/40</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.477</t>
+          <t>.466</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12014,7 +12014,7 @@
         <v>113</v>
       </c>
       <c r="G189" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H189" t="n">
         <v>25</v>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>11/42</t>
+          <t>12/43</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.466</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12056,16 +12056,16 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F190" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G190" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H190" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I190" t="n">
         <v>10</v>
@@ -12074,11 +12074,11 @@
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/33</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>8/35</t>
+          <t>9/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.493</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.821</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F182" t="n">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="G182" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="H182" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I182" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J182" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>11/37</t>
+          <t>16/33</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.865</t>
+          <t>.851</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F183" t="n">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="G183" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="H183" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I183" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J183" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K183" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>12/46</t>
+          <t>16/42</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.412</t>
+          <t>.399</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.795</t>
+          <t>.836</t>
         </is>
       </c>
       <c r="E184" t="n">
+        <v>25</v>
+      </c>
+      <c r="F184" t="n">
+        <v>230</v>
+      </c>
+      <c r="G184" t="n">
+        <v>80</v>
+      </c>
+      <c r="H184" t="n">
+        <v>49</v>
+      </c>
+      <c r="I184" t="n">
+        <v>27</v>
+      </c>
+      <c r="J184" t="n">
+        <v>9</v>
+      </c>
+      <c r="K184" t="n">
         <v>21</v>
       </c>
-      <c r="F184" t="n">
-        <v>182</v>
-      </c>
-      <c r="G184" t="n">
-        <v>61</v>
-      </c>
-      <c r="H184" t="n">
-        <v>27</v>
-      </c>
-      <c r="I184" t="n">
-        <v>17</v>
-      </c>
-      <c r="J184" t="n">
-        <v>6</v>
-      </c>
-      <c r="K184" t="n">
-        <v>19</v>
-      </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>12/44</t>
+          <t>17/42</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.472</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.677</t>
+          <t>.745</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F185" t="n">
-        <v>142</v>
+        <v>279</v>
       </c>
       <c r="G185" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H185" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="I185" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J185" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K185" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>10/48</t>
+          <t>17/47</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.454</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.818</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="G186" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H186" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I186" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J186" t="n">
         <v>6</v>
       </c>
       <c r="K186" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>10/42</t>
+          <t>11/39</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.484</t>
+          <t>.472</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.881</t>
+          <t>.849</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F187" t="n">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="G187" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="H187" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I187" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J187" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>13/46</t>
+          <t>16/42</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.450</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.913</t>
+          <t>.839</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F188" t="n">
-        <v>201</v>
+        <v>274</v>
       </c>
       <c r="G188" t="n">
+        <v>82</v>
+      </c>
+      <c r="H188" t="n">
         <v>63</v>
       </c>
-      <c r="H188" t="n">
-        <v>54</v>
-      </c>
       <c r="I188" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J188" t="n">
         <v>11</v>
       </c>
       <c r="K188" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>12/40</t>
+          <t>16/41</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.466</t>
+          <t>.435</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.769</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F189" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G189" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="H189" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I189" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J189" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K189" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>12/43</t>
+          <t>15/42</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.769</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>13</v>
       </c>
       <c r="F190" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="G190" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H190" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I190" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J190" t="n">
         <v>6</v>
       </c>
       <c r="K190" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>9/33</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.548</t>
+          <t>.536</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12107,13 +12107,13 @@
         <v>5</v>
       </c>
       <c r="F191" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G191" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H191" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I191" t="n">
         <v>14</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>9/36</t>
+          <t>9/35</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,25 +11663,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.506</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.807</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F182" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="G182" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H182" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I182" t="n">
         <v>9</v>
@@ -11690,11 +11690,11 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>16/33</t>
+          <t>18/35</t>
         </is>
       </c>
     </row>
@@ -11711,28 +11711,28 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.444</t>
+          <t>.436</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.851</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F183" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="G183" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H183" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I183" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J183" t="n">
         <v>15</v>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.399</t>
+          <t>.391</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.836</t>
+          <t>.826</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F184" t="n">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="G184" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H184" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I184" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J184" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K184" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>17/42</t>
+          <t>17/41</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.472</t>
+          <t>.477</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11816,16 +11816,16 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F185" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G185" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H185" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I185" t="n">
         <v>14</v>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>17/47</t>
+          <t>18/48</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.504</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11864,29 +11864,29 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F186" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="G186" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H186" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I186" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J186" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K186" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>11/39</t>
+          <t>11/37</t>
         </is>
       </c>
     </row>
@@ -11908,33 +11908,33 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.849</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F187" t="n">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="G187" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H187" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I187" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J187" t="n">
         <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>16/42</t>
+          <t>17/41</t>
         </is>
       </c>
     </row>
@@ -11951,25 +11951,25 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.450</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.839</t>
+          <t>.789</t>
         </is>
       </c>
       <c r="E188" t="n">
         <v>34</v>
       </c>
       <c r="F188" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="G188" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H188" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I188" t="n">
         <v>28</v>
@@ -11978,11 +11978,11 @@
         <v>11</v>
       </c>
       <c r="K188" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>16/41</t>
+          <t>17/41</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12017,7 @@
         <v>64</v>
       </c>
       <c r="H189" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I189" t="n">
         <v>7</v>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>15/42</t>
+          <t>16/43</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.484</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.756</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F190" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="G190" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H190" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I190" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J190" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K190" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.536</t>
+          <t>.563</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12107,19 +12107,19 @@
         <v>5</v>
       </c>
       <c r="F191" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G191" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H191" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I191" t="n">
         <v>14</v>
       </c>
       <c r="J191" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K191" t="n">
         <v>26</v>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,7 +11663,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.506</t>
+          <t>.512</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11672,10 +11672,10 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F182" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G182" t="n">
         <v>76</v>
@@ -11684,7 +11684,7 @@
         <v>40</v>
       </c>
       <c r="I182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J182" t="n">
         <v>6</v>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>18/35</t>
+          <t>20/38</t>
         </is>
       </c>
     </row>
@@ -11711,25 +11711,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.436</t>
+          <t>.439</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>20</v>
       </c>
       <c r="F183" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G183" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H183" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I183" t="n">
         <v>20</v>
@@ -11738,11 +11738,11 @@
         <v>15</v>
       </c>
       <c r="K183" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>16/42</t>
+          <t>17/43</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.391</t>
+          <t>.399</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11768,29 +11768,29 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F184" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="G184" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H184" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I184" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J184" t="n">
         <v>11</v>
       </c>
       <c r="K184" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>17/41</t>
+          <t>20/44</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.504</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.781</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F186" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="G186" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H186" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I186" t="n">
         <v>13</v>
       </c>
       <c r="J186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K186" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>11/37</t>
+          <t>14/40</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.472</t>
+          <t>.473</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.844</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F187" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G187" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H187" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I187" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J187" t="n">
         <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>17/41</t>
+          <t>20/46</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.454</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11960,16 +11960,16 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F188" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="G188" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H188" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I188" t="n">
         <v>28</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>17/41</t>
+          <t>18/42</t>
         </is>
       </c>
     </row>
@@ -12047,25 +12047,25 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.510</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.756</t>
+          <t>.760</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F190" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="G190" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H190" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I190" t="n">
         <v>14</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>14/34</t>
         </is>
       </c>
     </row>
@@ -12119,14 +12119,14 @@
         <v>14</v>
       </c>
       <c r="J191" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K191" t="n">
         <v>26</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>9/35</t>
+          <t>10/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.512</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.807</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F182" t="n">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="G182" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H182" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J182" t="n">
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>20/38</t>
+          <t>21/36</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.439</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>20</v>
       </c>
       <c r="F183" t="n">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="G183" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H183" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I183" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J183" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>17/43</t>
+          <t>18/41</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.399</t>
+          <t>.425</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.826</t>
+          <t>.805</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F184" t="n">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="G184" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="H184" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="I184" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J184" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K184" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>20/44</t>
+          <t>20/42</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.477</t>
+          <t>.493</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.745</t>
+          <t>.784</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F185" t="n">
-        <v>289</v>
+        <v>394</v>
       </c>
       <c r="G185" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="H185" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="I185" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J185" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K185" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>18/48</t>
+          <t>21/43</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.781</t>
+          <t>.795</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F186" t="n">
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="G186" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H186" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="I186" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J186" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K186" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>14/40</t>
+          <t>17/38</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.473</t>
+          <t>.454</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.844</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F187" t="n">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="G187" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="H187" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I187" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J187" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K187" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>20/46</t>
+          <t>22/45</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.454</t>
+          <t>.469</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.789</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F188" t="n">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="G188" t="n">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="H188" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I188" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J188" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K188" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>18/42</t>
+          <t>21/45</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.435</t>
+          <t>.419</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.740</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F189" t="n">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="G189" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H189" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="I189" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J189" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K189" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>16/43</t>
+          <t>18/40</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.510</t>
+          <t>.506</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.760</t>
+          <t>.774</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F190" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="G190" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H190" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I190" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K190" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>14/34</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.563</t>
+          <t>.559</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.744</t>
+          <t>.773</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F191" t="n">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="G191" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H191" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="I191" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J191" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K191" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>10/36</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,25 +11663,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.809</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F182" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="G182" t="n">
         <v>93</v>
       </c>
       <c r="H182" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I182" t="n">
         <v>11</v>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>21/36</t>
+          <t>23/38</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.469</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.809</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F183" t="n">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="G183" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="H183" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="I183" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J183" t="n">
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>18/41</t>
+          <t>20/39</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.425</t>
+          <t>.437</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.805</t>
+          <t>.791</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F184" t="n">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="G184" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H184" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I184" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J184" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K184" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>20/42</t>
+          <t>24/44</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.493</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.784</t>
+          <t>.778</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F185" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="G185" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H185" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I185" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J185" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K185" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>21/43</t>
+          <t>25/46</t>
         </is>
       </c>
     </row>
@@ -11855,22 +11855,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.457</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.795</t>
+          <t>.787</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F186" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="G186" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H186" t="n">
         <v>96</v>
@@ -11879,14 +11879,14 @@
         <v>19</v>
       </c>
       <c r="J186" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K186" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>17/38</t>
+          <t>20/40</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.454</t>
+          <t>.460</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.825</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F187" t="n">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="G187" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="H187" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I187" t="n">
         <v>21</v>
       </c>
       <c r="J187" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K187" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>22/45</t>
+          <t>24/44</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.469</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.734</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F188" t="n">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="G188" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H188" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I188" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J188" t="n">
         <v>14</v>
       </c>
       <c r="K188" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>21/45</t>
+          <t>25/48</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.419</t>
+          <t>.446</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.740</t>
+          <t>.741</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F189" t="n">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="G189" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H189" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I189" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J189" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K189" t="n">
         <v>26</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>18/40</t>
+          <t>24/45</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.506</t>
+          <t>.508</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.774</t>
+          <t>.767</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F190" t="n">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="G190" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H190" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I190" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J190" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K190" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/32</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.559</t>
+          <t>.547</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12107,26 +12107,26 @@
         <v>11</v>
       </c>
       <c r="F191" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="G191" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="H191" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I191" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J191" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K191" t="n">
         <v>38</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/34</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.469</t>
+          <t>.470</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.809</t>
+          <t>.821</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>24</v>
       </c>
       <c r="F183" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="G183" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H183" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I183" t="n">
         <v>29</v>
       </c>
       <c r="J183" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K183" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>20/39</t>
+          <t>25/44</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.437</t>
+          <t>.432</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11768,19 +11768,19 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F184" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G184" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H184" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I184" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J184" t="n">
         <v>16</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>24/44</t>
+          <t>26/46</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.495</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11819,13 +11819,13 @@
         <v>47</v>
       </c>
       <c r="F185" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G185" t="n">
         <v>122</v>
       </c>
       <c r="H185" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I185" t="n">
         <v>23</v>
@@ -11834,11 +11834,11 @@
         <v>16</v>
       </c>
       <c r="K185" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>25/46</t>
+          <t>26/47</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>20/40</t>
+          <t>21/41</t>
         </is>
       </c>
     </row>
@@ -11903,25 +11903,25 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.460</t>
+          <t>.453</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.825</t>
+          <t>.829</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F187" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G187" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H187" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I187" t="n">
         <v>21</v>
@@ -11930,11 +11930,11 @@
         <v>10</v>
       </c>
       <c r="K187" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>24/44</t>
+          <t>27/47</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.459</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11960,19 +11960,19 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F188" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G188" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H188" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I188" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J188" t="n">
         <v>14</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>25/48</t>
+          <t>26/49</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.446</t>
+          <t>.454</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.741</t>
+          <t>.732</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F189" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G189" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H189" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I189" t="n">
         <v>18</v>
       </c>
       <c r="J189" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K189" t="n">
         <v>26</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>24/45</t>
+          <t>25/46</t>
         </is>
       </c>
     </row>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.508</t>
+          <t>.513</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.767</t>
+          <t>.766</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>19</v>
       </c>
       <c r="F190" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G190" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H190" t="n">
         <v>53</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>18/32</t>
+          <t>19/33</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.547</t>
+          <t>.539</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12107,7 +12107,7 @@
         <v>11</v>
       </c>
       <c r="F191" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G191" t="n">
         <v>159</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>18/34</t>
+          <t>19/35</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.809</t>
+          <t>.814</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F182" t="n">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="G182" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="H182" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I182" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J182" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K182" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>23/38</t>
+          <t>25/38</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.470</t>
+          <t>.460</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.821</t>
+          <t>.807</t>
         </is>
       </c>
       <c r="E183" t="n">
         <v>24</v>
       </c>
       <c r="F183" t="n">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="G183" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H183" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="I183" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J183" t="n">
         <v>18</v>
       </c>
       <c r="K183" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>25/44</t>
+          <t>27/38</t>
         </is>
       </c>
     </row>
@@ -11759,28 +11759,28 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.432</t>
+          <t>.439</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.791</t>
+          <t>.796</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F184" t="n">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="G184" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H184" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I184" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J184" t="n">
         <v>16</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>26/46</t>
+          <t>26/43</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.493</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.778</t>
+          <t>.811</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="F185" t="n">
-        <v>418</v>
+        <v>543</v>
       </c>
       <c r="G185" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="H185" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="I185" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J185" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>26/47</t>
+          <t>30/42</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.457</t>
+          <t>.441</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.787</t>
+          <t>.796</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F186" t="n">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="G186" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H186" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I186" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J186" t="n">
         <v>15</v>
       </c>
       <c r="K186" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>21/41</t>
+          <t>23/40</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.453</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.829</t>
+          <t>.796</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F187" t="n">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="G187" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="H187" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I187" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J187" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K187" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>27/47</t>
+          <t>28/41</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.452</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.734</t>
+          <t>.756</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F188" t="n">
-        <v>452</v>
+        <v>554</v>
       </c>
       <c r="G188" t="n">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="H188" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="I188" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J188" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K188" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>26/49</t>
+          <t>29/43</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.454</t>
+          <t>.453</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.732</t>
+          <t>.701</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F189" t="n">
-        <v>281</v>
+        <v>330</v>
       </c>
       <c r="G189" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="H189" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I189" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J189" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K189" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>25/46</t>
+          <t>28/42</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.513</t>
+          <t>.507</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12056,16 +12056,16 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F190" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G190" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H190" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I190" t="n">
         <v>17</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>19/33</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.539</t>
+          <t>.561</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.773</t>
+          <t>.758</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F191" t="n">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="G191" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="H191" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I191" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J191" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K191" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>19/35</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,25 +11663,25 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.814</t>
+          <t>.822</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F182" t="n">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="G182" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H182" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I182" t="n">
         <v>14</v>
@@ -11690,7 +11690,7 @@
         <v>8</v>
       </c>
       <c r="K182" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.460</t>
+          <t>.474</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.807</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F183" t="n">
-        <v>381</v>
+        <v>493</v>
       </c>
       <c r="G183" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="H183" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="I183" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J183" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>27/38</t>
+          <t>31/42</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.439</t>
+          <t>.428</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.796</t>
+          <t>.792</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F184" t="n">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="G184" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="H184" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I184" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J184" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K184" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>26/43</t>
+          <t>26/41</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.493</t>
+          <t>.489</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.811</t>
+          <t>.794</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F185" t="n">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="G185" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H185" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I185" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J185" t="n">
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>30/42</t>
+          <t>33/45</t>
         </is>
       </c>
     </row>
@@ -11864,29 +11864,29 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F186" t="n">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="G186" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H186" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I186" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J186" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>23/40</t>
+          <t>23/38</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.467</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.796</t>
+          <t>.789</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F187" t="n">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="G187" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H187" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="I187" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J187" t="n">
         <v>12</v>
       </c>
       <c r="K187" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>28/41</t>
+          <t>30/42</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.452</t>
+          <t>.461</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.756</t>
+          <t>.780</t>
         </is>
       </c>
       <c r="E188" t="n">
+        <v>83</v>
+      </c>
+      <c r="F188" t="n">
+        <v>651</v>
+      </c>
+      <c r="G188" t="n">
+        <v>186</v>
+      </c>
+      <c r="H188" t="n">
+        <v>132</v>
+      </c>
+      <c r="I188" t="n">
+        <v>50</v>
+      </c>
+      <c r="J188" t="n">
+        <v>25</v>
+      </c>
+      <c r="K188" t="n">
         <v>65</v>
       </c>
-      <c r="F188" t="n">
-        <v>554</v>
-      </c>
-      <c r="G188" t="n">
-        <v>170</v>
-      </c>
-      <c r="H188" t="n">
-        <v>119</v>
-      </c>
-      <c r="I188" t="n">
-        <v>42</v>
-      </c>
-      <c r="J188" t="n">
-        <v>20</v>
-      </c>
-      <c r="K188" t="n">
-        <v>58</v>
-      </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>29/43</t>
+          <t>32/45</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.453</t>
+          <t>.459</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12008,29 +12008,29 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F189" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="G189" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H189" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I189" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J189" t="n">
         <v>15</v>
       </c>
       <c r="K189" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>28/42</t>
+          <t>30/45</t>
         </is>
       </c>
     </row>
@@ -12047,34 +12047,34 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.507</t>
+          <t>.488</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.766</t>
+          <t>.759</t>
         </is>
       </c>
       <c r="E190" t="n">
+        <v>26</v>
+      </c>
+      <c r="F190" t="n">
+        <v>340</v>
+      </c>
+      <c r="G190" t="n">
+        <v>107</v>
+      </c>
+      <c r="H190" t="n">
+        <v>62</v>
+      </c>
+      <c r="I190" t="n">
         <v>20</v>
       </c>
-      <c r="F190" t="n">
-        <v>279</v>
-      </c>
-      <c r="G190" t="n">
-        <v>90</v>
-      </c>
-      <c r="H190" t="n">
-        <v>56</v>
-      </c>
-      <c r="I190" t="n">
-        <v>17</v>
-      </c>
       <c r="J190" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K190" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.561</t>
+          <t>.550</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.758</t>
+          <t>.747</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F191" t="n">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="G191" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="H191" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I191" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J191" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K191" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/33</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,12 +11663,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.498</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.822</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -11678,7 +11678,7 @@
         <v>339</v>
       </c>
       <c r="G182" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H182" t="n">
         <v>60</v>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>25/38</t>
+          <t>26/39</t>
         </is>
       </c>
     </row>
@@ -11711,25 +11711,25 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.474</t>
+          <t>.481</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.839</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F183" t="n">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="G183" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H183" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I183" t="n">
         <v>39</v>
@@ -11738,11 +11738,11 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>31/42</t>
+          <t>33/44</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.428</t>
+          <t>.439</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.792</t>
+          <t>.780</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F184" t="n">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="G184" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H184" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I184" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J184" t="n">
         <v>18</v>
       </c>
       <c r="K184" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>26/41</t>
+          <t>29/44</t>
         </is>
       </c>
     </row>
@@ -11855,34 +11855,34 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.441</t>
+          <t>.442</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.796</t>
+          <t>.793</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F186" t="n">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="G186" t="n">
+        <v>120</v>
+      </c>
+      <c r="H186" t="n">
         <v>112</v>
       </c>
-      <c r="H186" t="n">
-        <v>107</v>
-      </c>
       <c r="I186" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J186" t="n">
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11903,25 +11903,25 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.467</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.789</t>
+          <t>.797</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F187" t="n">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="G187" t="n">
         <v>173</v>
       </c>
       <c r="H187" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I187" t="n">
         <v>27</v>
@@ -11930,11 +11930,11 @@
         <v>12</v>
       </c>
       <c r="K187" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>30/42</t>
+          <t>32/44</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.461</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.780</t>
+          <t>.788</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F188" t="n">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="G188" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H188" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I188" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J188" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K188" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>32/45</t>
+          <t>35/48</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12011,13 +12011,13 @@
         <v>42</v>
       </c>
       <c r="F189" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G189" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H189" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I189" t="n">
         <v>26</v>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>30/45</t>
+          <t>31/46</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.488</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12065,7 +12065,7 @@
         <v>107</v>
       </c>
       <c r="H190" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I190" t="n">
         <v>20</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>23/32</t>
         </is>
       </c>
     </row>
@@ -12095,22 +12095,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.550</t>
+          <t>.551</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.747</t>
+          <t>.742</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F191" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="G191" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H191" t="n">
         <v>94</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>23/33</t>
+          <t>26/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>33/44</t>
+          <t>34/45</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>29/44</t>
+          <t>31/46</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>33/45</t>
+          <t>34/47</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>23/38</t>
+          <t>26/42</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>32/44</t>
+          <t>33/45</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>35/48</t>
+          <t>36/49</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>31/46</t>
+          <t>31/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.498</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.824</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>339</v>
+        <v>437</v>
       </c>
       <c r="G182" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="H182" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I182" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J182" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K182" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>26/39</t>
+          <t>30/34</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.481</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.839</t>
+          <t>.849</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F183" t="n">
-        <v>508</v>
+        <v>580</v>
       </c>
       <c r="G183" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="H183" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="I183" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J183" t="n">
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>34/45</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.439</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11768,29 +11768,29 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F184" t="n">
-        <v>443</v>
+        <v>545</v>
       </c>
       <c r="G184" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="H184" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="I184" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J184" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K184" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>31/46</t>
+          <t>35/43</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.489</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.794</t>
+          <t>.810</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F185" t="n">
-        <v>568</v>
+        <v>623</v>
       </c>
       <c r="G185" t="n">
+        <v>179</v>
+      </c>
+      <c r="H185" t="n">
         <v>162</v>
       </c>
-      <c r="H185" t="n">
-        <v>152</v>
-      </c>
       <c r="I185" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J185" t="n">
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>34/47</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.442</t>
+          <t>.446</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.793</t>
+          <t>.781</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F186" t="n">
-        <v>349</v>
+        <v>421</v>
       </c>
       <c r="G186" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H186" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I186" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J186" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K186" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>26/42</t>
+          <t>31/41</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.467</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.797</t>
+          <t>.793</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F187" t="n">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="G187" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="H187" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I187" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J187" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K187" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>33/45</t>
+          <t>34/43</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.788</t>
+          <t>.781</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F188" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="G188" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H188" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I188" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J188" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K188" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>36/49</t>
+          <t>37/47</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.449</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.701</t>
+          <t>.723</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F189" t="n">
-        <v>351</v>
+        <v>439</v>
       </c>
       <c r="G189" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="H189" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I189" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J189" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K189" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>31/45</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.484</t>
+          <t>.498</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.759</t>
+          <t>.737</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F190" t="n">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="G190" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="H190" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I190" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J190" t="n">
         <v>12</v>
       </c>
       <c r="K190" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>23/32</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.551</t>
+          <t>.550</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.742</t>
+          <t>.737</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F191" t="n">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="G191" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="H191" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I191" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J191" t="n">
         <v>38</v>
       </c>
       <c r="K191" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>26/36</t>
+          <t>28/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,22 +11663,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.495</t>
+          <t>.490</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.824</t>
+          <t>.836</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F182" t="n">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="G182" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H182" t="n">
         <v>80</v>
@@ -11687,14 +11687,14 @@
         <v>21</v>
       </c>
       <c r="J182" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K182" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>30/34</t>
+          <t>35/39</t>
         </is>
       </c>
     </row>
@@ -11711,28 +11711,28 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.484</t>
+          <t>.482</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.849</t>
+          <t>.844</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F183" t="n">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="G183" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H183" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I183" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J183" t="n">
         <v>20</v>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>37/46</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.448</t>
+          <t>.450</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11768,29 +11768,29 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F184" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="G184" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H184" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I184" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J184" t="n">
         <v>25</v>
       </c>
       <c r="K184" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>35/43</t>
+          <t>38/46</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11816,29 +11816,29 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F185" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G185" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H185" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I185" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J185" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K185" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>39/48</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.446</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F186" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="G186" t="n">
         <v>160</v>
@@ -11882,11 +11882,11 @@
         <v>19</v>
       </c>
       <c r="K186" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>31/41</t>
+          <t>32/42</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.467</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.793</t>
+          <t>.799</t>
         </is>
       </c>
       <c r="E187" t="n">
         <v>44</v>
       </c>
       <c r="F187" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G187" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H187" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I187" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J187" t="n">
         <v>14</v>
       </c>
       <c r="K187" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>34/43</t>
+          <t>37/47</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.457</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11966,7 +11966,7 @@
         <v>685</v>
       </c>
       <c r="G188" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H188" t="n">
         <v>142</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>39/49</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.449</t>
+          <t>.446</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12014,13 +12014,13 @@
         <v>439</v>
       </c>
       <c r="G189" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H189" t="n">
         <v>84</v>
       </c>
       <c r="I189" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J189" t="n">
         <v>19</v>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>36/45</t>
         </is>
       </c>
     </row>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.498</t>
+          <t>.492</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.737</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>30</v>
       </c>
       <c r="F190" t="n">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G190" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H190" t="n">
         <v>83</v>
@@ -12071,14 +12071,14 @@
         <v>27</v>
       </c>
       <c r="J190" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K190" t="n">
         <v>56</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>29/34</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11663,38 +11663,38 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>.490</t>
+          <t>.479</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>.836</t>
+          <t>.844</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F182" t="n">
-        <v>448</v>
+        <v>522</v>
       </c>
       <c r="G182" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="H182" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="I182" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J182" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K182" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>35/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11711,38 +11711,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>.482</t>
+          <t>.492</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>.844</t>
+          <t>.824</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F183" t="n">
-        <v>588</v>
+        <v>742</v>
       </c>
       <c r="G183" t="n">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="H183" t="n">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="I183" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J183" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K183" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>37/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -11759,38 +11759,38 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>.450</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>.780</t>
+          <t>.771</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F184" t="n">
-        <v>550</v>
+        <v>634</v>
       </c>
       <c r="G184" t="n">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H184" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="I184" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J184" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K184" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>38/46</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -11807,38 +11807,38 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.483</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.810</t>
+          <t>.827</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="F185" t="n">
-        <v>628</v>
+        <v>761</v>
       </c>
       <c r="G185" t="n">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="H185" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="I185" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J185" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K185" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>39/48</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -11855,38 +11855,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.448</t>
+          <t>.460</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.781</t>
+          <t>.765</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F186" t="n">
-        <v>426</v>
+        <v>587</v>
       </c>
       <c r="G186" t="n">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="H186" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="I186" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J186" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K186" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>32/42</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11903,38 +11903,38 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>.799</t>
+          <t>.778</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F187" t="n">
-        <v>507</v>
+        <v>613</v>
       </c>
       <c r="G187" t="n">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="H187" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="I187" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J187" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.457</t>
+          <t>.459</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.781</t>
+          <t>.787</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="F188" t="n">
-        <v>685</v>
+        <v>856</v>
       </c>
       <c r="G188" t="n">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="H188" t="n">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="I188" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J188" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K188" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>39/49</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -11999,38 +11999,38 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.446</t>
+          <t>.465</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>.723</t>
+          <t>.738</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F189" t="n">
-        <v>439</v>
+        <v>562</v>
       </c>
       <c r="G189" t="n">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="H189" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="I189" t="n">
         <v>34</v>
       </c>
       <c r="J189" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>36/45</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12047,38 +12047,38 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.492</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.770</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F190" t="n">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="G190" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H190" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="I190" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J190" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K190" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>29/34</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -12095,38 +12095,38 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.550</t>
+          <t>.562</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.737</t>
+          <t>.777</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F191" t="n">
-        <v>421</v>
+        <v>573</v>
       </c>
       <c r="G191" t="n">
-        <v>213</v>
+        <v>265</v>
       </c>
       <c r="H191" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="I191" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J191" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K191" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>28/36</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11732,7 +11732,7 @@
         <v>193</v>
       </c>
       <c r="I183" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J183" t="n">
         <v>26</v>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -11774,10 +11774,10 @@
         <v>634</v>
       </c>
       <c r="G184" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H184" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I184" t="n">
         <v>64</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -11807,25 +11807,25 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.485</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.827</t>
+          <t>.829</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F185" t="n">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="G185" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H185" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I185" t="n">
         <v>34</v>
@@ -11834,11 +11834,11 @@
         <v>25</v>
       </c>
       <c r="K185" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -11855,28 +11855,28 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>.460</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.765</t>
+          <t>.770</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F186" t="n">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="G186" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H186" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I186" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J186" t="n">
         <v>33</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -11951,38 +11951,38 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.454</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>.787</t>
+          <t>.795</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F188" t="n">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="G188" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="H188" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I188" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J188" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K188" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>49/49</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>.465</t>
+          <t>.466</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -12011,10 +12011,10 @@
         <v>63</v>
       </c>
       <c r="F189" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G189" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H189" t="n">
         <v>113</v>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12047,25 +12047,25 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>.484</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.770</t>
+          <t>.777</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F190" t="n">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="G190" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H190" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I190" t="n">
         <v>28</v>
@@ -12074,11 +12074,11 @@
         <v>14</v>
       </c>
       <c r="K190" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>.562</t>
+          <t>.565</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12104,13 +12104,13 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F191" t="n">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="G191" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H191" t="n">
         <v>126</v>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11671,26 +11671,40 @@
           <t>.844</t>
         </is>
       </c>
-      <c r="E182" t="n">
-        <v>58</v>
-      </c>
-      <c r="F182" t="n">
-        <v>522</v>
-      </c>
-      <c r="G182" t="n">
-        <v>163</v>
-      </c>
-      <c r="H182" t="n">
-        <v>101</v>
-      </c>
-      <c r="I182" t="n">
-        <v>26</v>
-      </c>
-      <c r="J182" t="n">
-        <v>13</v>
-      </c>
-      <c r="K182" t="n">
-        <v>57</v>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -11719,26 +11733,40 @@
           <t>.824</t>
         </is>
       </c>
-      <c r="E183" t="n">
-        <v>50</v>
-      </c>
-      <c r="F183" t="n">
-        <v>742</v>
-      </c>
-      <c r="G183" t="n">
-        <v>276</v>
-      </c>
-      <c r="H183" t="n">
-        <v>193</v>
-      </c>
-      <c r="I183" t="n">
-        <v>58</v>
-      </c>
-      <c r="J183" t="n">
-        <v>26</v>
-      </c>
-      <c r="K183" t="n">
-        <v>89</v>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -11767,26 +11795,40 @@
           <t>.771</t>
         </is>
       </c>
-      <c r="E184" t="n">
-        <v>70</v>
-      </c>
-      <c r="F184" t="n">
-        <v>634</v>
-      </c>
-      <c r="G184" t="n">
-        <v>200</v>
-      </c>
-      <c r="H184" t="n">
-        <v>141</v>
-      </c>
-      <c r="I184" t="n">
-        <v>64</v>
-      </c>
-      <c r="J184" t="n">
-        <v>30</v>
-      </c>
-      <c r="K184" t="n">
-        <v>61</v>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -11815,26 +11857,40 @@
           <t>.829</t>
         </is>
       </c>
-      <c r="E185" t="n">
-        <v>94</v>
-      </c>
-      <c r="F185" t="n">
-        <v>784</v>
-      </c>
-      <c r="G185" t="n">
-        <v>229</v>
-      </c>
-      <c r="H185" t="n">
-        <v>188</v>
-      </c>
-      <c r="I185" t="n">
-        <v>34</v>
-      </c>
-      <c r="J185" t="n">
-        <v>25</v>
-      </c>
-      <c r="K185" t="n">
-        <v>83</v>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -11863,26 +11919,40 @@
           <t>.770</t>
         </is>
       </c>
-      <c r="E186" t="n">
-        <v>66</v>
-      </c>
-      <c r="F186" t="n">
-        <v>599</v>
-      </c>
-      <c r="G186" t="n">
-        <v>205</v>
-      </c>
-      <c r="H186" t="n">
-        <v>161</v>
-      </c>
-      <c r="I186" t="n">
-        <v>36</v>
-      </c>
-      <c r="J186" t="n">
-        <v>33</v>
-      </c>
-      <c r="K186" t="n">
-        <v>79</v>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11911,26 +11981,40 @@
           <t>.778</t>
         </is>
       </c>
-      <c r="E187" t="n">
-        <v>54</v>
-      </c>
-      <c r="F187" t="n">
-        <v>613</v>
-      </c>
-      <c r="G187" t="n">
-        <v>238</v>
-      </c>
-      <c r="H187" t="n">
-        <v>167</v>
-      </c>
-      <c r="I187" t="n">
-        <v>38</v>
-      </c>
-      <c r="J187" t="n">
-        <v>17</v>
-      </c>
-      <c r="K187" t="n">
-        <v>71</v>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -11959,26 +12043,40 @@
           <t>.795</t>
         </is>
       </c>
-      <c r="E188" t="n">
-        <v>116</v>
-      </c>
-      <c r="F188" t="n">
-        <v>876</v>
-      </c>
-      <c r="G188" t="n">
-        <v>257</v>
-      </c>
-      <c r="H188" t="n">
-        <v>182</v>
-      </c>
-      <c r="I188" t="n">
-        <v>64</v>
-      </c>
-      <c r="J188" t="n">
-        <v>36</v>
-      </c>
-      <c r="K188" t="n">
-        <v>100</v>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -12007,26 +12105,40 @@
           <t>.738</t>
         </is>
       </c>
-      <c r="E189" t="n">
-        <v>63</v>
-      </c>
-      <c r="F189" t="n">
-        <v>564</v>
-      </c>
-      <c r="G189" t="n">
-        <v>253</v>
-      </c>
-      <c r="H189" t="n">
-        <v>113</v>
-      </c>
-      <c r="I189" t="n">
-        <v>34</v>
-      </c>
-      <c r="J189" t="n">
-        <v>20</v>
-      </c>
-      <c r="K189" t="n">
-        <v>50</v>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -12055,26 +12167,40 @@
           <t>.777</t>
         </is>
       </c>
-      <c r="E190" t="n">
-        <v>33</v>
-      </c>
-      <c r="F190" t="n">
-        <v>501</v>
-      </c>
-      <c r="G190" t="n">
-        <v>157</v>
-      </c>
-      <c r="H190" t="n">
-        <v>107</v>
-      </c>
-      <c r="I190" t="n">
-        <v>28</v>
-      </c>
-      <c r="J190" t="n">
-        <v>14</v>
-      </c>
-      <c r="K190" t="n">
-        <v>62</v>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -12103,30 +12229,416 @@
           <t>.777</t>
         </is>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>36/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Ducksnation</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>.478</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>.864</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6</v>
+      </c>
+      <c r="F192" t="n">
+        <v>91</v>
+      </c>
+      <c r="G192" t="n">
+        <v>23</v>
+      </c>
+      <c r="H192" t="n">
+        <v>32</v>
+      </c>
+      <c r="I192" t="n">
+        <v>6</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
+        <v>5</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>6/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Flagg on the Play</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>.583</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>15</v>
+      </c>
+      <c r="G193" t="n">
+        <v>8</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>VJ's Generators ⚡️</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>.333</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>4</v>
+      </c>
+      <c r="G194" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>1/34</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Thomas's Team</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>.400</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>11</v>
+      </c>
+      <c r="G195" t="n">
+        <v>11</v>
+      </c>
+      <c r="H195" t="n">
+        <v>7</v>
+      </c>
+      <c r="I195" t="n">
+        <v>2</v>
+      </c>
+      <c r="J195" t="n">
+        <v>2</v>
+      </c>
+      <c r="K195" t="n">
+        <v>2</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>1/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Goat Club</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>.550</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>.857</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5</v>
+      </c>
+      <c r="F196" t="n">
+        <v>55</v>
+      </c>
+      <c r="G196" t="n">
+        <v>10</v>
+      </c>
+      <c r="H196" t="n">
+        <v>15</v>
+      </c>
+      <c r="I196" t="n">
+        <v>3</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>4</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Fab's Fascinating Team</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>.563</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>.824</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>10</v>
+      </c>
+      <c r="F197" t="n">
+        <v>104</v>
+      </c>
+      <c r="G197" t="n">
+        <v>38</v>
+      </c>
+      <c r="H197" t="n">
+        <v>35</v>
+      </c>
+      <c r="I197" t="n">
+        <v>4</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="n">
+        <v>11</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>3/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Jerome (Ty)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>.446</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>5</v>
+      </c>
+      <c r="F198" t="n">
+        <v>70</v>
+      </c>
+      <c r="G198" t="n">
         <v>28</v>
       </c>
-      <c r="F191" t="n">
-        <v>578</v>
-      </c>
-      <c r="G191" t="n">
-        <v>266</v>
-      </c>
-      <c r="H191" t="n">
-        <v>126</v>
-      </c>
-      <c r="I191" t="n">
-        <v>40</v>
-      </c>
-      <c r="J191" t="n">
-        <v>49</v>
-      </c>
-      <c r="K191" t="n">
-        <v>72</v>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>36/36</t>
+      <c r="H198" t="n">
+        <v>21</v>
+      </c>
+      <c r="I198" t="n">
+        <v>3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="n">
+        <v>4</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>YOU ARE MY BRONSHINE</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>0/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12423,7 +12423,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.400</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12432,16 +12432,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G195" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H195" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I195" t="n">
         <v>2</v>
@@ -12450,11 +12450,11 @@
         <v>2</v>
       </c>
       <c r="K195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>1/32</t>
+          <t>3/34</t>
         </is>
       </c>
     </row>
@@ -12471,38 +12471,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.550</t>
+          <t>.580</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.786</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F196" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G196" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H196" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -12519,38 +12519,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.563</t>
+          <t>.557</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.824</t>
+          <t>.792</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F197" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="G197" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H197" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I197" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J197" t="n">
         <v>3</v>
       </c>
       <c r="K197" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>3/41</t>
+          <t>7/45</t>
         </is>
       </c>
     </row>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.446</t>
+          <t>.477</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12576,29 +12576,29 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F198" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G198" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H198" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J198" t="n">
         <v>3</v>
       </c>
       <c r="K198" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2/45</t>
+          <t>4/46</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.478</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.864</t>
+          <t>.841</t>
         </is>
       </c>
       <c r="E192" t="n">
+        <v>23</v>
+      </c>
+      <c r="F192" t="n">
+        <v>238</v>
+      </c>
+      <c r="G192" t="n">
+        <v>55</v>
+      </c>
+      <c r="H192" t="n">
+        <v>64</v>
+      </c>
+      <c r="I192" t="n">
+        <v>12</v>
+      </c>
+      <c r="J192" t="n">
         <v>6</v>
       </c>
-      <c r="F192" t="n">
-        <v>91</v>
-      </c>
-      <c r="G192" t="n">
-        <v>23</v>
-      </c>
-      <c r="H192" t="n">
-        <v>32</v>
-      </c>
-      <c r="I192" t="n">
-        <v>6</v>
-      </c>
-      <c r="J192" t="n">
-        <v>2</v>
-      </c>
       <c r="K192" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>6/41</t>
+          <t>12/37</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.583</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.722</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F193" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="G193" t="n">
+        <v>61</v>
+      </c>
+      <c r="H193" t="n">
+        <v>33</v>
+      </c>
+      <c r="I193" t="n">
+        <v>6</v>
+      </c>
+      <c r="J193" t="n">
         <v>8</v>
       </c>
-      <c r="H193" t="n">
-        <v>1</v>
-      </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" t="n">
-        <v>3</v>
-      </c>
       <c r="K193" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2/41</t>
+          <t>7/33</t>
         </is>
       </c>
     </row>
@@ -12379,34 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.333</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>.492</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>.882</t>
+        </is>
+      </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F194" t="n">
+        <v>88</v>
+      </c>
+      <c r="G194" t="n">
+        <v>29</v>
+      </c>
+      <c r="H194" t="n">
+        <v>21</v>
+      </c>
+      <c r="I194" t="n">
         <v>4</v>
       </c>
-      <c r="G194" t="n">
-        <v>2</v>
-      </c>
-      <c r="H194" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>1/34</t>
+          <t>5/37</t>
         </is>
       </c>
     </row>
@@ -12423,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.889</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F195" t="n">
-        <v>16</v>
+        <v>225</v>
       </c>
       <c r="G195" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="H195" t="n">
+        <v>42</v>
+      </c>
+      <c r="I195" t="n">
         <v>9</v>
       </c>
-      <c r="I195" t="n">
-        <v>2</v>
-      </c>
       <c r="J195" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K195" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>3/34</t>
+          <t>10/33</t>
         </is>
       </c>
     </row>
@@ -12471,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.580</t>
+          <t>.504</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.786</t>
+          <t>.773</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="G196" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H196" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J196" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K196" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>10/35</t>
         </is>
       </c>
     </row>
@@ -12519,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.557</t>
+          <t>.553</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.792</t>
+          <t>.787</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F197" t="n">
-        <v>139</v>
+        <v>304</v>
       </c>
       <c r="G197" t="n">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="H197" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="I197" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J197" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K197" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>7/45</t>
+          <t>10/40</t>
         </is>
       </c>
     </row>
@@ -12567,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.477</t>
+          <t>.432</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.974</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F198" t="n">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="G198" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H198" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I198" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J198" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K198" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>4/46</t>
+          <t>6/35</t>
         </is>
       </c>
     </row>
@@ -12613,32 +12617,40 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>.553</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>.737</t>
+        </is>
+      </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J199" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K199" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>0/31</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12295,26 +12295,26 @@
         <v>23</v>
       </c>
       <c r="F192" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G192" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H192" t="n">
         <v>64</v>
       </c>
       <c r="I192" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J192" t="n">
         <v>6</v>
       </c>
       <c r="K192" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>12/37</t>
+          <t>12/36</t>
         </is>
       </c>
     </row>
@@ -12336,33 +12336,33 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.722</t>
+          <t>.650</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F193" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G193" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="H193" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J193" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K193" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>7/33</t>
+          <t>10/34</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.492</t>
+          <t>.423</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.882</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F194" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="G194" t="n">
+        <v>47</v>
+      </c>
+      <c r="H194" t="n">
         <v>29</v>
       </c>
-      <c r="H194" t="n">
-        <v>21</v>
-      </c>
       <c r="I194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J194" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K194" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>5/37</t>
+          <t>9/39</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.478</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.889</t>
+          <t>.907</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F195" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="G195" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H195" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I195" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J195" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K195" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>10/33</t>
+          <t>12/34</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.504</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.773</t>
+          <t>.824</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F196" t="n">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="G196" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H196" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I196" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K196" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>10/35</t>
+          <t>16/41</t>
         </is>
       </c>
     </row>
@@ -12523,25 +12523,25 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.553</t>
+          <t>.534</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.787</t>
+          <t>.811</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F197" t="n">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="G197" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H197" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I197" t="n">
         <v>11</v>
@@ -12550,11 +12550,11 @@
         <v>9</v>
       </c>
       <c r="K197" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>10/40</t>
+          <t>12/41</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.432</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.974</t>
+          <t>.860</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F198" t="n">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="G198" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H198" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I198" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J198" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K198" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>6/35</t>
+          <t>11/40</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.553</t>
+          <t>.534</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.737</t>
+          <t>.761</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F199" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="G199" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H199" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I199" t="n">
+        <v>7</v>
+      </c>
+      <c r="J199" t="n">
         <v>5</v>
       </c>
-      <c r="J199" t="n">
-        <v>4</v>
-      </c>
       <c r="K199" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12314,7 +12314,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>12/36</t>
+          <t>13/37</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12343,26 +12343,26 @@
         <v>15</v>
       </c>
       <c r="F193" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G193" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H193" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I193" t="n">
         <v>7</v>
       </c>
       <c r="J193" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K193" t="n">
         <v>18</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>10/34</t>
+          <t>12/36</t>
         </is>
       </c>
     </row>
@@ -12384,20 +12384,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.816</t>
         </is>
       </c>
       <c r="E194" t="n">
         <v>12</v>
       </c>
       <c r="F194" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G194" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H194" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I194" t="n">
         <v>5</v>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>9/39</t>
+          <t>11/41</t>
         </is>
       </c>
     </row>
@@ -12427,25 +12427,25 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.478</t>
+          <t>.481</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.907</t>
+          <t>.897</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F195" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G195" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H195" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I195" t="n">
         <v>13</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>12/34</t>
+          <t>13/35</t>
         </is>
       </c>
     </row>
@@ -12523,25 +12523,25 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.534</t>
+          <t>.538</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.811</t>
+          <t>.793</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F197" t="n">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="G197" t="n">
         <v>118</v>
       </c>
       <c r="H197" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I197" t="n">
         <v>11</v>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>12/41</t>
+          <t>13/42</t>
         </is>
       </c>
     </row>
@@ -12634,10 +12634,10 @@
         <v>177</v>
       </c>
       <c r="G199" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H199" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I199" t="n">
         <v>7</v>
@@ -12646,11 +12646,11 @@
         <v>5</v>
       </c>
       <c r="K199" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,34 +12283,34 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.841</t>
+          <t>.850</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F192" t="n">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="G192" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H192" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="I192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K192" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -12427,34 +12427,34 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.481</t>
+          <t>.473</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.897</t>
+          <t>.896</t>
         </is>
       </c>
       <c r="E195" t="n">
         <v>32</v>
       </c>
       <c r="F195" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G195" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H195" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I195" t="n">
         <v>13</v>
       </c>
       <c r="J195" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K195" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -12475,34 +12475,34 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.483</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.824</t>
+          <t>.812</t>
         </is>
       </c>
       <c r="E196" t="n">
+        <v>18</v>
+      </c>
+      <c r="F196" t="n">
+        <v>174</v>
+      </c>
+      <c r="G196" t="n">
+        <v>58</v>
+      </c>
+      <c r="H196" t="n">
+        <v>47</v>
+      </c>
+      <c r="I196" t="n">
+        <v>11</v>
+      </c>
+      <c r="J196" t="n">
+        <v>9</v>
+      </c>
+      <c r="K196" t="n">
         <v>19</v>
-      </c>
-      <c r="F196" t="n">
-        <v>193</v>
-      </c>
-      <c r="G196" t="n">
-        <v>63</v>
-      </c>
-      <c r="H196" t="n">
-        <v>49</v>
-      </c>
-      <c r="I196" t="n">
-        <v>13</v>
-      </c>
-      <c r="J196" t="n">
-        <v>10</v>
-      </c>
-      <c r="K196" t="n">
-        <v>21</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -12523,34 +12523,34 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.538</t>
+          <t>.524</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.793</t>
+          <t>.795</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F197" t="n">
-        <v>352</v>
+        <v>258</v>
       </c>
       <c r="G197" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="H197" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="I197" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J197" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K197" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -12571,34 +12571,34 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.444</t>
+          <t>.452</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.860</t>
+          <t>.829</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="G198" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H198" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I198" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J198" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.482</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.850</t>
+          <t>.862</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F192" t="n">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="G192" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="H192" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I192" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K192" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>13/37</t>
+          <t>16/39</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.650</t>
+          <t>.689</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F193" t="n">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="G193" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H193" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I193" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J193" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K193" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>12/36</t>
+          <t>16/45</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.423</t>
+          <t>.492</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.816</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F194" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="G194" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H194" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="I194" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J194" t="n">
         <v>6</v>
       </c>
       <c r="K194" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>11/41</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.473</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12436,29 +12436,29 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F195" t="n">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="G195" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="H195" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I195" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J195" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K195" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>13/35</t>
+          <t>14/33</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.480</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.812</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F196" t="n">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="G196" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="H196" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="I196" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J196" t="n">
         <v>9</v>
       </c>
       <c r="K196" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>16/41</t>
+          <t>16/34</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.524</t>
+          <t>.513</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.795</t>
+          <t>.825</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F197" t="n">
-        <v>258</v>
+        <v>356</v>
       </c>
       <c r="G197" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="H197" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I197" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J197" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K197" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>13/42</t>
+          <t>16/38</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.452</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.829</t>
+          <t>.787</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F198" t="n">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="G198" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H198" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I198" t="n">
+        <v>14</v>
+      </c>
+      <c r="J198" t="n">
         <v>8</v>
       </c>
-      <c r="J198" t="n">
-        <v>7</v>
-      </c>
       <c r="K198" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>11/40</t>
+          <t>13/38</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.534</t>
+          <t>.529</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.761</t>
+          <t>.686</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F199" t="n">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G199" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H199" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I199" t="n">
+        <v>10</v>
+      </c>
+      <c r="J199" t="n">
         <v>7</v>
       </c>
-      <c r="J199" t="n">
-        <v>5</v>
-      </c>
       <c r="K199" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.482</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12292,16 +12292,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F192" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G192" t="n">
+        <v>65</v>
+      </c>
+      <c r="H192" t="n">
         <v>64</v>
-      </c>
-      <c r="H192" t="n">
-        <v>63</v>
       </c>
       <c r="I192" t="n">
         <v>14</v>
@@ -12310,7 +12310,7 @@
         <v>5</v>
       </c>
       <c r="K192" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -12336,20 +12336,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.689</t>
+          <t>.702</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F193" t="n">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="G193" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H193" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I193" t="n">
         <v>12</v>
@@ -12358,11 +12358,11 @@
         <v>13</v>
       </c>
       <c r="K193" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>16/45</t>
+          <t>17/46</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.492</t>
+          <t>.526</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.864</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F194" t="n">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="G194" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H194" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I194" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J194" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K194" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/41</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.896</t>
+          <t>.901</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F195" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="G195" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H195" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I195" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J195" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K195" t="n">
         <v>42</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>14/33</t>
+          <t>18/37</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.480</t>
+          <t>.504</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.870</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F196" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="G196" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H196" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I196" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J196" t="n">
         <v>9</v>
       </c>
       <c r="K196" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>16/34</t>
+          <t>23/43</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.513</t>
+          <t>.515</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.825</t>
+          <t>.826</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F197" t="n">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="G197" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="H197" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I197" t="n">
         <v>20</v>
       </c>
       <c r="J197" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K197" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>16/38</t>
+          <t>21/43</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.495</t>
+          <t>.504</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.787</t>
+          <t>.813</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F198" t="n">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="G198" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H198" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I198" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J198" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K198" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>13/38</t>
+          <t>17/42</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.529</t>
+          <t>.523</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.686</t>
+          <t>.702</t>
         </is>
       </c>
       <c r="E199" t="n">
         <v>19</v>
       </c>
       <c r="F199" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G199" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H199" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I199" t="n">
         <v>10</v>
       </c>
       <c r="J199" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K199" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12314,7 +12314,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>16/39</t>
+          <t>17/40</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>17/46</t>
+          <t>18/47</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>14/41</t>
+          <t>16/43</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>17/42</t>
+          <t>18/43</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.489</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.862</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F192" t="n">
-        <v>302</v>
+        <v>441</v>
       </c>
       <c r="G192" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="H192" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="I192" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K192" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>17/40</t>
+          <t>23/36</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.702</t>
+          <t>.726</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F193" t="n">
-        <v>247</v>
+        <v>355</v>
       </c>
       <c r="G193" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="H193" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="I193" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J193" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K193" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>18/47</t>
+          <t>25/46</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.526</t>
+          <t>.490</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.864</t>
+          <t>.872</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F194" t="n">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="G194" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H194" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I194" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J194" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K194" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>16/43</t>
+          <t>22/41</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.448</t>
+          <t>.450</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.901</t>
+          <t>.835</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F195" t="n">
-        <v>339</v>
+        <v>446</v>
       </c>
       <c r="G195" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="H195" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I195" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J195" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K195" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>18/37</t>
+          <t>23/40</t>
         </is>
       </c>
     </row>
@@ -12480,33 +12480,33 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.870</t>
+          <t>.872</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F196" t="n">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="G196" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H196" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I196" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J196" t="n">
         <v>9</v>
       </c>
       <c r="K196" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>23/43</t>
+          <t>26/42</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.515</t>
+          <t>.513</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.826</t>
+          <t>.835</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F197" t="n">
-        <v>372</v>
+        <v>440</v>
       </c>
       <c r="G197" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="H197" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="I197" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J197" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K197" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>21/43</t>
+          <t>22/41</t>
         </is>
       </c>
     </row>
@@ -12576,33 +12576,33 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.813</t>
+          <t>.845</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F198" t="n">
-        <v>323</v>
+        <v>396</v>
       </c>
       <c r="G198" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H198" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I198" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J198" t="n">
         <v>9</v>
       </c>
       <c r="K198" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>18/43</t>
+          <t>19/41</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.523</t>
+          <t>.518</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.702</t>
+          <t>.713</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F199" t="n">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="G199" t="n">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="H199" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I199" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J199" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K199" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.489</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.860</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>45</v>
       </c>
       <c r="F192" t="n">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="G192" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H192" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I192" t="n">
         <v>26</v>
       </c>
       <c r="J192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K192" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>23/36</t>
+          <t>27/40</t>
         </is>
       </c>
     </row>
@@ -12331,25 +12331,25 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.726</t>
+          <t>.711</t>
         </is>
       </c>
       <c r="E193" t="n">
         <v>28</v>
       </c>
       <c r="F193" t="n">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="G193" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H193" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I193" t="n">
         <v>19</v>
@@ -12379,25 +12379,25 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.490</t>
+          <t>.502</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.872</t>
+          <t>.873</t>
         </is>
       </c>
       <c r="E194" t="n">
         <v>25</v>
       </c>
       <c r="F194" t="n">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G194" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H194" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I194" t="n">
         <v>14</v>
@@ -12406,11 +12406,11 @@
         <v>10</v>
       </c>
       <c r="K194" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>22/41</t>
+          <t>23/42</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.450</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.835</t>
+          <t>.845</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F195" t="n">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="G195" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H195" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I195" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J195" t="n">
         <v>18</v>
       </c>
       <c r="K195" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>23/40</t>
+          <t>24/41</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.504</t>
+          <t>.508</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12484,16 +12484,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F196" t="n">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G196" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H196" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I196" t="n">
         <v>19</v>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.513</t>
+          <t>.523</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.835</t>
+          <t>.843</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F197" t="n">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="G197" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H197" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="I197" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J197" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K197" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>22/41</t>
+          <t>24/43</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.504</t>
+          <t>.505</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.845</t>
+          <t>.862</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F198" t="n">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="G198" t="n">
+        <v>108</v>
+      </c>
+      <c r="H198" t="n">
         <v>101</v>
-      </c>
-      <c r="H198" t="n">
-        <v>98</v>
       </c>
       <c r="I198" t="n">
         <v>21</v>
       </c>
       <c r="J198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K198" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>19/41</t>
+          <t>22/44</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.518</t>
+          <t>.505</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.713</t>
+          <t>.726</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F199" t="n">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="G199" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H199" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I199" t="n">
         <v>12</v>
       </c>
       <c r="J199" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K199" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12362,7 +12362,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>25/46</t>
+          <t>26/47</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>23/42</t>
+          <t>24/43</t>
         </is>
       </c>
     </row>
@@ -12439,7 +12439,7 @@
         <v>57</v>
       </c>
       <c r="F195" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G195" t="n">
         <v>142</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>24/41</t>
+          <t>25/42</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>26/42</t>
+          <t>27/43</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>24/43</t>
+          <t>26/45</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>22/44</t>
+          <t>23/45</t>
         </is>
       </c>
     </row>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.860</t>
+          <t>.862</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F192" t="n">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="G192" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H192" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I192" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J192" t="n">
         <v>11</v>
       </c>
       <c r="K192" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>27/40</t>
+          <t>29/40</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.495</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.711</t>
+          <t>.726</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F193" t="n">
-        <v>372</v>
+        <v>501</v>
       </c>
       <c r="G193" t="n">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="H193" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="I193" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J193" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K193" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>26/47</t>
+          <t>32/45</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.502</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.873</t>
+          <t>.872</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F194" t="n">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="G194" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="H194" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="I194" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J194" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K194" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>24/43</t>
+          <t>26/41</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.461</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.845</t>
+          <t>.839</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F195" t="n">
-        <v>489</v>
+        <v>578</v>
       </c>
       <c r="G195" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="H195" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="I195" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J195" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K195" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>25/42</t>
+          <t>30/39</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.508</t>
+          <t>.519</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.872</t>
+          <t>.863</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F196" t="n">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="G196" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H196" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I196" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K196" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>27/43</t>
+          <t>30/43</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.523</t>
+          <t>.520</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.843</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F197" t="n">
-        <v>487</v>
+        <v>597</v>
       </c>
       <c r="G197" t="n">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="H197" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="I197" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J197" t="n">
         <v>19</v>
       </c>
       <c r="K197" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>26/45</t>
+          <t>32/43</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.505</t>
+          <t>.507</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.862</t>
+          <t>.860</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F198" t="n">
-        <v>442</v>
+        <v>556</v>
       </c>
       <c r="G198" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="H198" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="I198" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J198" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K198" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>23/45</t>
+          <t>27/41</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.505</t>
+          <t>.492</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.726</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F199" t="n">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="G199" t="n">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="H199" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I199" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J199" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K199" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.507</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.862</t>
+          <t>.865</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F192" t="n">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="G192" t="n">
         <v>119</v>
       </c>
       <c r="H192" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I192" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J192" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K192" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>29/40</t>
+          <t>30/41</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.726</t>
+          <t>.727</t>
         </is>
       </c>
       <c r="E193" t="n">
         <v>42</v>
       </c>
       <c r="F193" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="G193" t="n">
         <v>214</v>
       </c>
       <c r="H193" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I193" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J193" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K193" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>32/45</t>
+          <t>34/47</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.507</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.872</t>
+          <t>.867</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F194" t="n">
-        <v>374</v>
+        <v>423</v>
       </c>
       <c r="G194" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H194" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="I194" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J194" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K194" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>26/41</t>
+          <t>31/46</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.461</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12436,13 +12436,13 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F195" t="n">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="G195" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H195" t="n">
         <v>108</v>
@@ -12454,11 +12454,11 @@
         <v>23</v>
       </c>
       <c r="K195" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>30/39</t>
+          <t>32/41</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.519</t>
+          <t>.513</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.863</t>
+          <t>.860</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F196" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="G196" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H196" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I196" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J196" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K196" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>30/43</t>
+          <t>32/45</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.520</t>
+          <t>.525</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.835</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F197" t="n">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="G197" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H197" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I197" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J197" t="n">
         <v>19</v>
       </c>
       <c r="K197" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>32/43</t>
+          <t>34/45</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.507</t>
+          <t>.501</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.860</t>
+          <t>.861</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F198" t="n">
-        <v>556</v>
+        <v>599</v>
       </c>
       <c r="G198" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H198" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I198" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J198" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K198" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>27/41</t>
+          <t>32/46</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.492</t>
+          <t>.482</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12628,16 +12628,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F199" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="G199" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H199" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I199" t="n">
         <v>14</v>
@@ -12646,11 +12646,11 @@
         <v>15</v>
       </c>
       <c r="K199" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12314,7 +12314,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>30/41</t>
+          <t>30/42</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.507</t>
+          <t>.488</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.865</t>
+          <t>.885</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F192" t="n">
-        <v>496</v>
+        <v>602</v>
       </c>
       <c r="G192" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="H192" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I192" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J192" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K192" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>30/42</t>
+          <t>37/42</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12340,29 +12340,29 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F193" t="n">
-        <v>516</v>
+        <v>588</v>
       </c>
       <c r="G193" t="n">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="H193" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="I193" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J193" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K193" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>34/47</t>
+          <t>39/47</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.507</t>
+          <t>.506</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.867</t>
+          <t>.876</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F194" t="n">
-        <v>423</v>
+        <v>483</v>
       </c>
       <c r="G194" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="H194" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="I194" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J194" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>31/46</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.443</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.839</t>
+          <t>.810</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F195" t="n">
-        <v>583</v>
+        <v>684</v>
       </c>
       <c r="G195" t="n">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="H195" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I195" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="J195" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K195" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>32/41</t>
+          <t>39/42</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.513</t>
+          <t>.499</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.860</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F196" t="n">
-        <v>414</v>
+        <v>521</v>
       </c>
       <c r="G196" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="H196" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="I196" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J196" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K196" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>32/45</t>
+          <t>40/44</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.525</t>
+          <t>.531</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.835</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F197" t="n">
-        <v>625</v>
+        <v>715</v>
       </c>
       <c r="G197" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="H197" t="n">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I197" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J197" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K197" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>34/45</t>
+          <t>37/44</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.501</t>
+          <t>.486</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.861</t>
+          <t>.854</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F198" t="n">
-        <v>599</v>
+        <v>653</v>
       </c>
       <c r="G198" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="H198" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="I198" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J198" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K198" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>32/46</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.482</t>
+          <t>.490</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.760</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F199" t="n">
-        <v>348</v>
+        <v>416</v>
       </c>
       <c r="G199" t="n">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="H199" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="I199" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J199" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K199" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>29/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,22 +12283,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.488</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.885</t>
+          <t>.880</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>60</v>
       </c>
       <c r="F192" t="n">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="G192" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H192" t="n">
         <v>122</v>
@@ -12307,14 +12307,14 @@
         <v>43</v>
       </c>
       <c r="J192" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>37/42</t>
+          <t>38/43</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.506</t>
+          <t>.513</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.876</t>
+          <t>.879</t>
         </is>
       </c>
       <c r="E194" t="n">
         <v>42</v>
       </c>
       <c r="F194" t="n">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="G194" t="n">
         <v>148</v>
       </c>
       <c r="H194" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I194" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J194" t="n">
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>36/45</t>
         </is>
       </c>
     </row>
@@ -12523,25 +12523,25 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.531</t>
+          <t>.535</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.820</t>
         </is>
       </c>
       <c r="E197" t="n">
         <v>62</v>
       </c>
       <c r="F197" t="n">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="G197" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H197" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I197" t="n">
         <v>38</v>
@@ -12550,11 +12550,11 @@
         <v>21</v>
       </c>
       <c r="K197" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>37/44</t>
+          <t>38/45</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.486</t>
+          <t>.482</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.854</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F198" t="n">
-        <v>653</v>
+        <v>692</v>
       </c>
       <c r="G198" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H198" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I198" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J198" t="n">
         <v>19</v>
       </c>
       <c r="K198" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>38/47</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,38 +12283,38 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.478</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.880</t>
+          <t>.875</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F192" t="n">
-        <v>607</v>
+        <v>694</v>
       </c>
       <c r="G192" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="H192" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="I192" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J192" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K192" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>38/43</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12331,38 +12331,38 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>.495</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>.727</t>
+          <t>.728</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F193" t="n">
-        <v>588</v>
+        <v>708</v>
       </c>
       <c r="G193" t="n">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="H193" t="n">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="I193" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J193" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K193" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>39/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.513</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.879</t>
+          <t>.855</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F194" t="n">
-        <v>502</v>
+        <v>640</v>
       </c>
       <c r="G194" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="H194" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="I194" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J194" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K194" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>36/45</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12427,38 +12427,38 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>.443</t>
+          <t>.453</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.810</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F195" t="n">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="G195" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="H195" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="I195" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J195" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K195" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>39/42</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12475,38 +12475,38 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>.499</t>
+          <t>.501</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.829</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F196" t="n">
-        <v>521</v>
+        <v>572</v>
       </c>
       <c r="G196" t="n">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="H196" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="I196" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J196" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K196" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>40/44</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12523,38 +12523,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>.535</t>
+          <t>.532</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>.820</t>
+          <t>.839</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F197" t="n">
-        <v>727</v>
+        <v>836</v>
       </c>
       <c r="G197" t="n">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="H197" t="n">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="I197" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J197" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K197" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>38/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12571,38 +12571,38 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.482</t>
+          <t>.471</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.833</t>
+          <t>.827</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F198" t="n">
-        <v>692</v>
+        <v>781</v>
       </c>
       <c r="G198" t="n">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="H198" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="I198" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J198" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K198" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>38/47</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12619,38 +12619,38 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>.490</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.760</t>
+          <t>.768</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F199" t="n">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="G199" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H199" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I199" t="n">
         <v>21</v>
       </c>
       <c r="J199" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K199" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>29/31</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>.478</t>
+          <t>.480</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12295,7 +12295,7 @@
         <v>70</v>
       </c>
       <c r="F192" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G192" t="n">
         <v>194</v>
@@ -12304,17 +12304,17 @@
         <v>149</v>
       </c>
       <c r="I192" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J192" t="n">
         <v>21</v>
       </c>
       <c r="K192" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12379,38 +12379,38 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>.855</t>
+          <t>.851</t>
         </is>
       </c>
       <c r="E194" t="n">
         <v>55</v>
       </c>
       <c r="F194" t="n">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="G194" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H194" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I194" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J194" t="n">
         <v>27</v>
       </c>
       <c r="K194" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -12535,10 +12535,10 @@
         <v>70</v>
       </c>
       <c r="F197" t="n">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="G197" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H197" t="n">
         <v>238</v>
@@ -12550,11 +12550,11 @@
         <v>23</v>
       </c>
       <c r="K197" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>.471</t>
+          <t>.470</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12291,26 +12291,40 @@
           <t>.875</t>
         </is>
       </c>
-      <c r="E192" t="n">
-        <v>70</v>
-      </c>
-      <c r="F192" t="n">
-        <v>698</v>
-      </c>
-      <c r="G192" t="n">
-        <v>194</v>
-      </c>
-      <c r="H192" t="n">
-        <v>149</v>
-      </c>
-      <c r="I192" t="n">
-        <v>51</v>
-      </c>
-      <c r="J192" t="n">
-        <v>21</v>
-      </c>
-      <c r="K192" t="n">
-        <v>70</v>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -12339,26 +12353,40 @@
           <t>.728</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>56</v>
-      </c>
-      <c r="F193" t="n">
-        <v>708</v>
-      </c>
-      <c r="G193" t="n">
-        <v>278</v>
-      </c>
-      <c r="H193" t="n">
-        <v>191</v>
-      </c>
-      <c r="I193" t="n">
-        <v>38</v>
-      </c>
-      <c r="J193" t="n">
-        <v>36</v>
-      </c>
-      <c r="K193" t="n">
-        <v>79</v>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -12387,26 +12415,40 @@
           <t>.851</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v>55</v>
-      </c>
-      <c r="F194" t="n">
-        <v>655</v>
-      </c>
-      <c r="G194" t="n">
-        <v>197</v>
-      </c>
-      <c r="H194" t="n">
-        <v>167</v>
-      </c>
-      <c r="I194" t="n">
-        <v>38</v>
-      </c>
-      <c r="J194" t="n">
-        <v>27</v>
-      </c>
-      <c r="K194" t="n">
-        <v>97</v>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -12435,26 +12477,40 @@
           <t>.800</t>
         </is>
       </c>
-      <c r="E195" t="n">
-        <v>100</v>
-      </c>
-      <c r="F195" t="n">
-        <v>764</v>
-      </c>
-      <c r="G195" t="n">
-        <v>233</v>
-      </c>
-      <c r="H195" t="n">
-        <v>151</v>
-      </c>
-      <c r="I195" t="n">
-        <v>55</v>
-      </c>
-      <c r="J195" t="n">
-        <v>35</v>
-      </c>
-      <c r="K195" t="n">
-        <v>94</v>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -12483,26 +12539,40 @@
           <t>.829</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>71</v>
-      </c>
-      <c r="F196" t="n">
-        <v>572</v>
-      </c>
-      <c r="G196" t="n">
-        <v>184</v>
-      </c>
-      <c r="H196" t="n">
-        <v>133</v>
-      </c>
-      <c r="I196" t="n">
-        <v>33</v>
-      </c>
-      <c r="J196" t="n">
-        <v>16</v>
-      </c>
-      <c r="K196" t="n">
-        <v>62</v>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -12531,26 +12601,40 @@
           <t>.839</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>70</v>
-      </c>
-      <c r="F197" t="n">
-        <v>838</v>
-      </c>
-      <c r="G197" t="n">
-        <v>293</v>
-      </c>
-      <c r="H197" t="n">
-        <v>238</v>
-      </c>
-      <c r="I197" t="n">
-        <v>44</v>
-      </c>
-      <c r="J197" t="n">
-        <v>23</v>
-      </c>
-      <c r="K197" t="n">
-        <v>92</v>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -12579,26 +12663,40 @@
           <t>.827</t>
         </is>
       </c>
-      <c r="E198" t="n">
-        <v>79</v>
-      </c>
-      <c r="F198" t="n">
-        <v>781</v>
-      </c>
-      <c r="G198" t="n">
-        <v>239</v>
-      </c>
-      <c r="H198" t="n">
-        <v>180</v>
-      </c>
-      <c r="I198" t="n">
-        <v>50</v>
-      </c>
-      <c r="J198" t="n">
-        <v>23</v>
-      </c>
-      <c r="K198" t="n">
-        <v>89</v>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -12627,30 +12725,428 @@
           <t>.768</t>
         </is>
       </c>
-      <c r="E199" t="n">
-        <v>42</v>
-      </c>
-      <c r="F199" t="n">
-        <v>448</v>
-      </c>
-      <c r="G199" t="n">
-        <v>201</v>
-      </c>
-      <c r="H199" t="n">
-        <v>102</v>
-      </c>
-      <c r="I199" t="n">
-        <v>21</v>
-      </c>
-      <c r="J199" t="n">
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>31/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Ducksnation</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>.466</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>.944</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>20</v>
+      </c>
+      <c r="F200" t="n">
+        <v>119</v>
+      </c>
+      <c r="G200" t="n">
+        <v>29</v>
+      </c>
+      <c r="H200" t="n">
         <v>22</v>
       </c>
-      <c r="K199" t="n">
-        <v>59</v>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>31/31</t>
+      <c r="I200" t="n">
+        <v>7</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>13</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>5/45</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>YOU ARE MY BRONSHINE</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>.538</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>.714</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>7</v>
+      </c>
+      <c r="F201" t="n">
+        <v>87</v>
+      </c>
+      <c r="G201" t="n">
+        <v>47</v>
+      </c>
+      <c r="H201" t="n">
+        <v>17</v>
+      </c>
+      <c r="I201" t="n">
+        <v>4</v>
+      </c>
+      <c r="J201" t="n">
+        <v>7</v>
+      </c>
+      <c r="K201" t="n">
+        <v>10</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>VJ's Generators ⚡️</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>.410</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>.727</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>5</v>
+      </c>
+      <c r="F202" t="n">
+        <v>53</v>
+      </c>
+      <c r="G202" t="n">
+        <v>20</v>
+      </c>
+      <c r="H202" t="n">
+        <v>15</v>
+      </c>
+      <c r="I202" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" t="n">
+        <v>2</v>
+      </c>
+      <c r="K202" t="n">
+        <v>6</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>4/38</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Goat Club</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>.550</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>.938</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>61</v>
+      </c>
+      <c r="G203" t="n">
+        <v>20</v>
+      </c>
+      <c r="H203" t="n">
+        <v>11</v>
+      </c>
+      <c r="I203" t="n">
+        <v>4</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="n">
+        <v>10</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Flagg on the Play</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>.367</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>.667</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" t="n">
+        <v>63</v>
+      </c>
+      <c r="G204" t="n">
+        <v>36</v>
+      </c>
+      <c r="H204" t="n">
+        <v>20</v>
+      </c>
+      <c r="I204" t="n">
+        <v>4</v>
+      </c>
+      <c r="J204" t="n">
+        <v>6</v>
+      </c>
+      <c r="K204" t="n">
+        <v>11</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>4/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Jerome (Ty)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>.514</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>.853</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>4</v>
+      </c>
+      <c r="F205" t="n">
+        <v>71</v>
+      </c>
+      <c r="G205" t="n">
+        <v>19</v>
+      </c>
+      <c r="H205" t="n">
+        <v>12</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>8</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>4/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Thomas's Team</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>.459</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>.909</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>15</v>
+      </c>
+      <c r="F206" t="n">
+        <v>103</v>
+      </c>
+      <c r="G206" t="n">
+        <v>25</v>
+      </c>
+      <c r="H206" t="n">
+        <v>18</v>
+      </c>
+      <c r="I206" t="n">
+        <v>6</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>9</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>5/32</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Fab's Fascinating Team</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>.507</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>8</v>
+      </c>
+      <c r="F207" t="n">
+        <v>94</v>
+      </c>
+      <c r="G207" t="n">
+        <v>33</v>
+      </c>
+      <c r="H207" t="n">
+        <v>29</v>
+      </c>
+      <c r="I207" t="n">
+        <v>7</v>
+      </c>
+      <c r="J207" t="n">
+        <v>2</v>
+      </c>
+      <c r="K207" t="n">
+        <v>10</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>5/41</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.466</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.944</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E200" t="n">
         <v>20</v>
       </c>
       <c r="F200" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G200" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H200" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I200" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K200" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>5/45</t>
+          <t>7/47</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.538</t>
+          <t>.529</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.714</t>
+          <t>.682</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F201" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="G201" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H201" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I201" t="n">
         <v>4</v>
       </c>
       <c r="J201" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K201" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/32</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.550</t>
+          <t>.522</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12935,10 +12935,10 @@
         <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G203" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H203" t="n">
         <v>11</v>
@@ -12950,11 +12950,11 @@
         <v>3</v>
       </c>
       <c r="K203" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2/32</t>
+          <t>4/34</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.367</t>
+          <t>.397</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12983,10 +12983,10 @@
         <v>3</v>
       </c>
       <c r="F204" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G204" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H204" t="n">
         <v>20</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>4/43</t>
+          <t>5/44</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>4/40</t>
+          <t>5/41</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -13076,29 +13076,29 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F206" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G206" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H206" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J206" t="n">
         <v>1</v>
       </c>
       <c r="K206" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>5/32</t>
+          <t>7/34</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.507</t>
+          <t>.481</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -13127,16 +13127,16 @@
         <v>8</v>
       </c>
       <c r="F207" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G207" t="n">
         <v>33</v>
       </c>
       <c r="H207" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I207" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J207" t="n">
         <v>2</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>5/41</t>
+          <t>6/42</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13098,7 +13098,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>7/34</t>
+          <t>7/38</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.466</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.828</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F200" t="n">
-        <v>126</v>
+        <v>262</v>
       </c>
       <c r="G200" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="H200" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I200" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J200" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>7/47</t>
+          <t>14/46</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.529</t>
+          <t>.520</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.682</t>
+          <t>.718</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F201" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="G201" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="H201" t="n">
+        <v>35</v>
+      </c>
+      <c r="I201" t="n">
+        <v>7</v>
+      </c>
+      <c r="J201" t="n">
+        <v>12</v>
+      </c>
+      <c r="K201" t="n">
         <v>21</v>
       </c>
-      <c r="I201" t="n">
-        <v>4</v>
-      </c>
-      <c r="J201" t="n">
-        <v>11</v>
-      </c>
-      <c r="K201" t="n">
-        <v>15</v>
-      </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>8/32</t>
+          <t>10/33</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.410</t>
+          <t>.393</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.727</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E202" t="n">
+        <v>10</v>
+      </c>
+      <c r="F202" t="n">
+        <v>104</v>
+      </c>
+      <c r="G202" t="n">
+        <v>48</v>
+      </c>
+      <c r="H202" t="n">
+        <v>24</v>
+      </c>
+      <c r="I202" t="n">
         <v>5</v>
       </c>
-      <c r="F202" t="n">
-        <v>53</v>
-      </c>
-      <c r="G202" t="n">
-        <v>20</v>
-      </c>
-      <c r="H202" t="n">
-        <v>15</v>
-      </c>
-      <c r="I202" t="n">
-        <v>3</v>
-      </c>
       <c r="J202" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K202" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>4/38</t>
+          <t>11/37</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.522</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.938</t>
+          <t>.927</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F203" t="n">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G203" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="H203" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="I203" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J203" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K203" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>4/34</t>
+          <t>12/43</t>
         </is>
       </c>
     </row>
@@ -12971,38 +12971,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.397</t>
+          <t>.469</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.667</t>
+          <t>.740</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F204" t="n">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="G204" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="H204" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J204" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K204" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>5/44</t>
+          <t>13/44</t>
         </is>
       </c>
     </row>
@@ -13019,38 +13019,38 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.514</t>
+          <t>.538</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.853</t>
+          <t>.869</t>
         </is>
       </c>
       <c r="E205" t="n">
+        <v>8</v>
+      </c>
+      <c r="F205" t="n">
+        <v>145</v>
+      </c>
+      <c r="G205" t="n">
+        <v>40</v>
+      </c>
+      <c r="H205" t="n">
+        <v>31</v>
+      </c>
+      <c r="I205" t="n">
         <v>4</v>
       </c>
-      <c r="F205" t="n">
-        <v>71</v>
-      </c>
-      <c r="G205" t="n">
-        <v>19</v>
-      </c>
-      <c r="H205" t="n">
-        <v>12</v>
-      </c>
-      <c r="I205" t="n">
-        <v>1</v>
-      </c>
       <c r="J205" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K205" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>5/41</t>
+          <t>10/45</t>
         </is>
       </c>
     </row>
@@ -13067,38 +13067,38 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.413</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.909</t>
+          <t>.875</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F206" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="G206" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H206" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I206" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K206" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>7/38</t>
+          <t>13/40</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.481</t>
+          <t>.543</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>.966</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F207" t="n">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="G207" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="H207" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I207" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J207" t="n">
         <v>2</v>
       </c>
       <c r="K207" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>6/42</t>
+          <t>10/43</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.466</t>
+          <t>.472</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12788,10 +12788,10 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F200" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G200" t="n">
         <v>86</v>
@@ -12806,11 +12806,11 @@
         <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>14/46</t>
+          <t>15/47</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.520</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12836,29 +12836,29 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F201" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G201" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H201" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I201" t="n">
         <v>7</v>
       </c>
       <c r="J201" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K201" t="n">
         <v>21</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>10/33</t>
+          <t>12/35</t>
         </is>
       </c>
     </row>
@@ -12875,28 +12875,28 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.393</t>
+          <t>.380</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.750</t>
+          <t>.743</t>
         </is>
       </c>
       <c r="E202" t="n">
         <v>10</v>
       </c>
       <c r="F202" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G202" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H202" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I202" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J202" t="n">
         <v>9</v>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>11/37</t>
+          <t>14/40</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
         <v>47</v>
       </c>
       <c r="I203" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J203" t="n">
         <v>10</v>
@@ -13019,25 +13019,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.538</t>
+          <t>.532</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.869</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E205" t="n">
         <v>8</v>
       </c>
       <c r="F205" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G205" t="n">
         <v>40</v>
       </c>
       <c r="H205" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I205" t="n">
         <v>4</v>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>10/45</t>
+          <t>11/46</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.413</t>
+          <t>.410</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -13076,29 +13076,29 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F206" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G206" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H206" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I206" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J206" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K206" t="n">
         <v>14</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>13/40</t>
+          <t>14/41</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.543</t>
+          <t>.551</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.966</t>
+          <t>.968</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F207" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="G207" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H207" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I207" t="n">
         <v>12</v>
       </c>
       <c r="J207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K207" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>10/43</t>
+          <t>12/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.472</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.828</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F200" t="n">
-        <v>267</v>
+        <v>431</v>
       </c>
       <c r="G200" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="H200" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I200" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J200" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K200" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>15/47</t>
+          <t>24/46</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.542</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.718</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F201" t="n">
-        <v>176</v>
+        <v>309</v>
       </c>
       <c r="G201" t="n">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="H201" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="I201" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J201" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K201" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>12/35</t>
+          <t>17/35</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.380</t>
+          <t>.425</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.743</t>
+          <t>.770</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="G202" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="H202" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I202" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J202" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K202" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>14/40</t>
+          <t>21/42</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.483</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.927</t>
+          <t>.843</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F203" t="n">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="G203" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="H203" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I203" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J203" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K203" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>12/43</t>
+          <t>14/40</t>
         </is>
       </c>
     </row>
@@ -12971,38 +12971,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.469</t>
+          <t>.466</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.740</t>
+          <t>.769</t>
         </is>
       </c>
       <c r="E204" t="n">
+        <v>23</v>
+      </c>
+      <c r="F204" t="n">
+        <v>293</v>
+      </c>
+      <c r="G204" t="n">
+        <v>118</v>
+      </c>
+      <c r="H204" t="n">
+        <v>74</v>
+      </c>
+      <c r="I204" t="n">
         <v>16</v>
       </c>
-      <c r="F204" t="n">
-        <v>205</v>
-      </c>
-      <c r="G204" t="n">
-        <v>87</v>
-      </c>
-      <c r="H204" t="n">
-        <v>48</v>
-      </c>
-      <c r="I204" t="n">
-        <v>8</v>
-      </c>
       <c r="J204" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K204" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>13/44</t>
+          <t>20/39</t>
         </is>
       </c>
     </row>
@@ -13024,33 +13024,33 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.870</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F205" t="n">
-        <v>146</v>
+        <v>309</v>
       </c>
       <c r="G205" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="H205" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="I205" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J205" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K205" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>11/46</t>
+          <t>21/45</t>
         </is>
       </c>
     </row>
@@ -13067,38 +13067,38 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.410</t>
+          <t>.423</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.875</t>
+          <t>.818</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F206" t="n">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="G206" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="H206" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I206" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J206" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K206" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>14/41</t>
+          <t>19/40</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.551</t>
+          <t>.525</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.968</t>
+          <t>.882</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F207" t="n">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="G207" t="n">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H207" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="I207" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J207" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K207" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>12/45</t>
+          <t>20/44</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.542</t>
+          <t>.548</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.810</t>
         </is>
       </c>
       <c r="E201" t="n">
+        <v>20</v>
+      </c>
+      <c r="F201" t="n">
+        <v>326</v>
+      </c>
+      <c r="G201" t="n">
+        <v>120</v>
+      </c>
+      <c r="H201" t="n">
+        <v>68</v>
+      </c>
+      <c r="I201" t="n">
         <v>19</v>
-      </c>
-      <c r="F201" t="n">
-        <v>309</v>
-      </c>
-      <c r="G201" t="n">
-        <v>117</v>
-      </c>
-      <c r="H201" t="n">
-        <v>65</v>
-      </c>
-      <c r="I201" t="n">
-        <v>18</v>
       </c>
       <c r="J201" t="n">
         <v>16</v>
       </c>
       <c r="K201" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>17/35</t>
+          <t>19/37</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.510</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.843</t>
+          <t>.830</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F203" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="G203" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H203" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I203" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J203" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K203" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>14/40</t>
+          <t>17/43</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.466</t>
+          <t>.468</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12983,26 +12983,26 @@
         <v>23</v>
       </c>
       <c r="F204" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G204" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H204" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I204" t="n">
         <v>16</v>
       </c>
       <c r="J204" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K204" t="n">
         <v>40</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>20/39</t>
+          <t>21/40</t>
         </is>
       </c>
     </row>
@@ -13067,25 +13067,25 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.423</t>
+          <t>.427</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.818</t>
+          <t>.812</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F206" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="G206" t="n">
+        <v>74</v>
+      </c>
+      <c r="H206" t="n">
         <v>70</v>
-      </c>
-      <c r="H206" t="n">
-        <v>66</v>
       </c>
       <c r="I206" t="n">
         <v>23</v>
@@ -13094,11 +13094,11 @@
         <v>6</v>
       </c>
       <c r="K206" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>19/40</t>
+          <t>21/42</t>
         </is>
       </c>
     </row>
@@ -13115,25 +13115,25 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.525</t>
+          <t>.526</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.882</t>
+          <t>.887</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F207" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="G207" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H207" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I207" t="n">
         <v>22</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>20/44</t>
+          <t>21/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13002,7 +13002,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>21/40</t>
+          <t>21/42</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.845</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F200" t="n">
-        <v>431</v>
+        <v>491</v>
       </c>
       <c r="G200" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H200" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I200" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J200" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K200" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>24/46</t>
+          <t>29/45</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.548</t>
+          <t>.537</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.810</t>
+          <t>.828</t>
         </is>
       </c>
       <c r="E201" t="n">
+        <v>25</v>
+      </c>
+      <c r="F201" t="n">
+        <v>392</v>
+      </c>
+      <c r="G201" t="n">
+        <v>151</v>
+      </c>
+      <c r="H201" t="n">
+        <v>70</v>
+      </c>
+      <c r="I201" t="n">
+        <v>26</v>
+      </c>
+      <c r="J201" t="n">
         <v>20</v>
       </c>
-      <c r="F201" t="n">
-        <v>326</v>
-      </c>
-      <c r="G201" t="n">
-        <v>120</v>
-      </c>
-      <c r="H201" t="n">
-        <v>68</v>
-      </c>
-      <c r="I201" t="n">
-        <v>19</v>
-      </c>
-      <c r="J201" t="n">
-        <v>16</v>
-      </c>
       <c r="K201" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>19/37</t>
+          <t>24/37</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.425</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.770</t>
+          <t>.761</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F202" t="n">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="G202" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="H202" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I202" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J202" t="n">
         <v>15</v>
       </c>
       <c r="K202" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>21/42</t>
+          <t>24/37</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.510</t>
+          <t>.502</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.830</t>
+          <t>.823</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F203" t="n">
-        <v>278</v>
+        <v>394</v>
       </c>
       <c r="G203" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="H203" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="I203" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J203" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K203" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>17/43</t>
+          <t>25/42</t>
         </is>
       </c>
     </row>
@@ -12971,38 +12971,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.468</t>
+          <t>.455</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.769</t>
+          <t>.747</t>
         </is>
       </c>
       <c r="E204" t="n">
+        <v>35</v>
+      </c>
+      <c r="F204" t="n">
+        <v>412</v>
+      </c>
+      <c r="G204" t="n">
+        <v>153</v>
+      </c>
+      <c r="H204" t="n">
+        <v>101</v>
+      </c>
+      <c r="I204" t="n">
         <v>23</v>
       </c>
-      <c r="F204" t="n">
-        <v>295</v>
-      </c>
-      <c r="G204" t="n">
-        <v>120</v>
-      </c>
-      <c r="H204" t="n">
-        <v>75</v>
-      </c>
-      <c r="I204" t="n">
-        <v>16</v>
-      </c>
       <c r="J204" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K204" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>21/42</t>
+          <t>27/43</t>
         </is>
       </c>
     </row>
@@ -13019,38 +13019,38 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.532</t>
+          <t>.524</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.870</t>
+          <t>.850</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F205" t="n">
-        <v>309</v>
+        <v>394</v>
       </c>
       <c r="G205" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="H205" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I205" t="n">
+        <v>14</v>
+      </c>
+      <c r="J205" t="n">
         <v>11</v>
       </c>
-      <c r="J205" t="n">
-        <v>10</v>
-      </c>
       <c r="K205" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>21/45</t>
+          <t>25/44</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.427</t>
+          <t>.435</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -13076,29 +13076,29 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F206" t="n">
-        <v>295</v>
+        <v>453</v>
       </c>
       <c r="G206" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="H206" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I206" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K206" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>21/42</t>
+          <t>27/43</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.526</t>
+          <t>.528</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.887</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F207" t="n">
-        <v>360</v>
+        <v>434</v>
       </c>
       <c r="G207" t="n">
+        <v>143</v>
+      </c>
+      <c r="H207" t="n">
         <v>125</v>
       </c>
-      <c r="H207" t="n">
-        <v>110</v>
-      </c>
       <c r="I207" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K207" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>21/45</t>
+          <t>25/43</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>29/45</t>
+          <t>30/47</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.448</t>
+          <t>.468</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.761</t>
+          <t>.756</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F202" t="n">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="G202" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H202" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I202" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J202" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K202" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>24/37</t>
+          <t>29/42</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>25/42</t>
+          <t>26/43</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.455</t>
+          <t>.453</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12983,26 +12983,26 @@
         <v>35</v>
       </c>
       <c r="F204" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G204" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H204" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I204" t="n">
         <v>23</v>
       </c>
       <c r="J204" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K204" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>27/43</t>
+          <t>29/45</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>25/44</t>
+          <t>28/48</t>
         </is>
       </c>
     </row>
@@ -13067,28 +13067,28 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.435</t>
+          <t>.441</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.812</t>
+          <t>.814</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F206" t="n">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="G206" t="n">
         <v>109</v>
       </c>
       <c r="H206" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I206" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J206" t="n">
         <v>8</v>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>27/43</t>
+          <t>28/44</t>
         </is>
       </c>
     </row>
@@ -13120,17 +13120,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.852</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F207" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="G207" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H207" t="n">
         <v>125</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>25/43</t>
+          <t>26/44</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.482</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.845</t>
+          <t>.832</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F200" t="n">
-        <v>491</v>
+        <v>555</v>
       </c>
       <c r="G200" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="H200" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I200" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J200" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K200" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>30/47</t>
+          <t>34/46</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.537</t>
+          <t>.526</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.828</t>
+          <t>.804</t>
         </is>
       </c>
       <c r="E201" t="n">
         <v>25</v>
       </c>
       <c r="F201" t="n">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="G201" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="H201" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="I201" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J201" t="n">
         <v>20</v>
       </c>
       <c r="K201" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>24/37</t>
+          <t>28/37</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.468</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.756</t>
+          <t>.758</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F202" t="n">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="G202" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="H202" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I202" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J202" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K202" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>29/42</t>
+          <t>32/43</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.502</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.823</t>
+          <t>.830</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F203" t="n">
-        <v>394</v>
+        <v>475</v>
       </c>
       <c r="G203" t="n">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="H203" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="I203" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J203" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K203" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>26/43</t>
+          <t>31/43</t>
         </is>
       </c>
     </row>
@@ -12971,38 +12971,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.453</t>
+          <t>.452</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.747</t>
+          <t>.757</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F204" t="n">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="G204" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H204" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="I204" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J204" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K204" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>29/45</t>
+          <t>31/43</t>
         </is>
       </c>
     </row>
@@ -13019,38 +13019,38 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.524</t>
+          <t>.521</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.850</t>
+          <t>.848</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F205" t="n">
-        <v>394</v>
+        <v>489</v>
       </c>
       <c r="G205" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H205" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I205" t="n">
+        <v>19</v>
+      </c>
+      <c r="J205" t="n">
         <v>14</v>
       </c>
-      <c r="J205" t="n">
-        <v>11</v>
-      </c>
       <c r="K205" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>28/48</t>
+          <t>31/45</t>
         </is>
       </c>
     </row>
@@ -13067,38 +13067,38 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.441</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.814</t>
+          <t>.837</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F206" t="n">
-        <v>470</v>
+        <v>564</v>
       </c>
       <c r="G206" t="n">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="H206" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="I206" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J206" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K206" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>28/44</t>
+          <t>33/48</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.528</t>
+          <t>.532</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.852</t>
+          <t>.818</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F207" t="n">
-        <v>448</v>
+        <v>567</v>
       </c>
       <c r="G207" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="H207" t="n">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="I207" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J207" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K207" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>26/44</t>
+          <t>32/44</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.452</t>
+          <t>.451</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12980,13 +12980,13 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F204" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="G204" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H204" t="n">
         <v>126</v>
@@ -12998,11 +12998,11 @@
         <v>30</v>
       </c>
       <c r="K204" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>31/43</t>
+          <t>33/45</t>
         </is>
       </c>
     </row>
@@ -13019,25 +13019,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.521</t>
+          <t>.525</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.848</t>
+          <t>.853</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F205" t="n">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="G205" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H205" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I205" t="n">
         <v>19</v>
@@ -13046,11 +13046,11 @@
         <v>14</v>
       </c>
       <c r="K205" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>31/45</t>
+          <t>33/47</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.444</t>
+          <t>.443</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -13079,13 +13079,13 @@
         <v>88</v>
       </c>
       <c r="F206" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G206" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H206" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I206" t="n">
         <v>40</v>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>33/48</t>
+          <t>34/49</t>
         </is>
       </c>
     </row>
@@ -13115,28 +13115,28 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.532</t>
+          <t>.531</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.818</t>
+          <t>.808</t>
         </is>
       </c>
       <c r="E207" t="n">
         <v>50</v>
       </c>
       <c r="F207" t="n">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="G207" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H207" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I207" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J207" t="n">
         <v>13</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>32/44</t>
+          <t>35/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12779,38 +12779,38 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>.482</t>
+          <t>.484</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.832</t>
+          <t>.825</t>
         </is>
       </c>
       <c r="E200" t="n">
+        <v>77</v>
+      </c>
+      <c r="F200" t="n">
+        <v>708</v>
+      </c>
+      <c r="G200" t="n">
+        <v>222</v>
+      </c>
+      <c r="H200" t="n">
+        <v>109</v>
+      </c>
+      <c r="I200" t="n">
+        <v>51</v>
+      </c>
+      <c r="J200" t="n">
+        <v>22</v>
+      </c>
+      <c r="K200" t="n">
         <v>67</v>
       </c>
-      <c r="F200" t="n">
-        <v>555</v>
-      </c>
-      <c r="G200" t="n">
-        <v>164</v>
-      </c>
-      <c r="H200" t="n">
-        <v>81</v>
-      </c>
-      <c r="I200" t="n">
-        <v>40</v>
-      </c>
-      <c r="J200" t="n">
-        <v>17</v>
-      </c>
-      <c r="K200" t="n">
-        <v>52</v>
-      </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>34/46</t>
+          <t>43/46</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.526</t>
+          <t>.536</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.804</t>
+          <t>.811</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F201" t="n">
-        <v>443</v>
+        <v>550</v>
       </c>
       <c r="G201" t="n">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="H201" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="I201" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J201" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K201" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>28/37</t>
+          <t>36/37</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.456</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.758</t>
+          <t>.775</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F202" t="n">
-        <v>350</v>
+        <v>411</v>
       </c>
       <c r="G202" t="n">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="H202" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="I202" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J202" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K202" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>32/43</t>
+          <t>35/38</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.491</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.830</t>
+          <t>.811</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F203" t="n">
-        <v>475</v>
+        <v>620</v>
       </c>
       <c r="G203" t="n">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="H203" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="I203" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J203" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K203" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>31/43</t>
+          <t>40/42</t>
         </is>
       </c>
     </row>
@@ -12971,38 +12971,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>.451</t>
+          <t>.461</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.757</t>
+          <t>.755</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F204" t="n">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="G204" t="n">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="H204" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="I204" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J204" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K204" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>33/45</t>
+          <t>41/43</t>
         </is>
       </c>
     </row>
@@ -13019,38 +13019,38 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.525</t>
+          <t>.516</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.853</t>
+          <t>.854</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F205" t="n">
-        <v>506</v>
+        <v>649</v>
       </c>
       <c r="G205" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="H205" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="I205" t="n">
+        <v>25</v>
+      </c>
+      <c r="J205" t="n">
         <v>19</v>
       </c>
-      <c r="J205" t="n">
-        <v>14</v>
-      </c>
       <c r="K205" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>33/47</t>
+          <t>38/45</t>
         </is>
       </c>
     </row>
@@ -13067,38 +13067,38 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.443</t>
+          <t>.455</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.837</t>
+          <t>.808</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="F206" t="n">
-        <v>570</v>
+        <v>738</v>
       </c>
       <c r="G206" t="n">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="H206" t="n">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="I206" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J206" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K206" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>34/49</t>
+          <t>40/47</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.531</t>
+          <t>.519</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.808</t>
+          <t>.811</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F207" t="n">
-        <v>576</v>
+        <v>649</v>
       </c>
       <c r="G207" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="H207" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I207" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J207" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K207" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>35/48</t>
+          <t>41/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>43/46</t>
+          <t>44/47</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.456</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.775</t>
+          <t>.758</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F202" t="n">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="G202" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H202" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I202" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J202" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K202" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>35/38</t>
+          <t>40/43</t>
         </is>
       </c>
     </row>
@@ -12932,16 +12932,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F203" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G203" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H203" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I203" t="n">
         <v>40</v>
@@ -12950,11 +12950,11 @@
         <v>27</v>
       </c>
       <c r="K203" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>40/42</t>
+          <t>41/43</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>41/43</t>
+          <t>42/44</t>
         </is>
       </c>
     </row>
@@ -13019,25 +13019,25 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>.516</t>
+          <t>.512</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>.854</t>
+          <t>.850</t>
         </is>
       </c>
       <c r="E205" t="n">
         <v>57</v>
       </c>
       <c r="F205" t="n">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G205" t="n">
         <v>177</v>
       </c>
       <c r="H205" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I205" t="n">
         <v>25</v>
@@ -13046,11 +13046,11 @@
         <v>19</v>
       </c>
       <c r="K205" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>38/45</t>
+          <t>41/48</t>
         </is>
       </c>
     </row>
@@ -13067,25 +13067,25 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.455</t>
+          <t>.456</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.808</t>
+          <t>.799</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F206" t="n">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="G206" t="n">
         <v>196</v>
       </c>
       <c r="H206" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I206" t="n">
         <v>53</v>
@@ -13094,11 +13094,11 @@
         <v>16</v>
       </c>
       <c r="K206" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>40/47</t>
+          <t>42/49</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12810,7 +12810,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>44/47</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12827,38 +12827,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>.536</t>
+          <t>.525</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>.811</t>
+          <t>.802</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F201" t="n">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="G201" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H201" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I201" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J201" t="n">
         <v>26</v>
       </c>
       <c r="K201" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>36/37</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -12875,38 +12875,38 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.461</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>.758</t>
+          <t>.772</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F202" t="n">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="G202" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="H202" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="I202" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J202" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K202" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>40/43</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12923,38 +12923,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.495</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.811</t>
+          <t>.822</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F203" t="n">
-        <v>623</v>
+        <v>658</v>
       </c>
       <c r="G203" t="n">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="H203" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I203" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J203" t="n">
         <v>27</v>
       </c>
       <c r="K203" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>41/43</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12976,33 +12976,33 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>.755</t>
+          <t>.759</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F204" t="n">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="G204" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H204" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I204" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J204" t="n">
         <v>38</v>
       </c>
       <c r="K204" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>42/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -13028,29 +13028,29 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F205" t="n">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="G205" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="H205" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I205" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J205" t="n">
         <v>19</v>
       </c>
       <c r="K205" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>41/48</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -13067,38 +13067,38 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>.456</t>
+          <t>.471</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.799</t>
+          <t>.793</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F206" t="n">
-        <v>747</v>
+        <v>841</v>
       </c>
       <c r="G206" t="n">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="H206" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="I206" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J206" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K206" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>42/49</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>
@@ -13115,38 +13115,38 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>.519</t>
+          <t>.524</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>.811</t>
+          <t>.814</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F207" t="n">
-        <v>649</v>
+        <v>770</v>
       </c>
       <c r="G207" t="n">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="H207" t="n">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="I207" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J207" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K207" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>41/48</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12787,26 +12787,40 @@
           <t>.825</t>
         </is>
       </c>
-      <c r="E200" t="n">
-        <v>77</v>
-      </c>
-      <c r="F200" t="n">
-        <v>708</v>
-      </c>
-      <c r="G200" t="n">
-        <v>222</v>
-      </c>
-      <c r="H200" t="n">
-        <v>109</v>
-      </c>
-      <c r="I200" t="n">
-        <v>51</v>
-      </c>
-      <c r="J200" t="n">
-        <v>22</v>
-      </c>
-      <c r="K200" t="n">
-        <v>67</v>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -12835,26 +12849,40 @@
           <t>.802</t>
         </is>
       </c>
-      <c r="E201" t="n">
-        <v>30</v>
-      </c>
-      <c r="F201" t="n">
-        <v>559</v>
-      </c>
-      <c r="G201" t="n">
-        <v>246</v>
-      </c>
-      <c r="H201" t="n">
-        <v>117</v>
-      </c>
-      <c r="I201" t="n">
-        <v>42</v>
-      </c>
-      <c r="J201" t="n">
-        <v>26</v>
-      </c>
-      <c r="K201" t="n">
-        <v>69</v>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -12883,26 +12911,40 @@
           <t>.772</t>
         </is>
       </c>
-      <c r="E202" t="n">
-        <v>42</v>
-      </c>
-      <c r="F202" t="n">
-        <v>491</v>
-      </c>
-      <c r="G202" t="n">
-        <v>203</v>
-      </c>
-      <c r="H202" t="n">
-        <v>120</v>
-      </c>
-      <c r="I202" t="n">
-        <v>30</v>
-      </c>
-      <c r="J202" t="n">
-        <v>27</v>
-      </c>
-      <c r="K202" t="n">
-        <v>57</v>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -12931,26 +12973,40 @@
           <t>.822</t>
         </is>
       </c>
-      <c r="E203" t="n">
-        <v>67</v>
-      </c>
-      <c r="F203" t="n">
-        <v>658</v>
-      </c>
-      <c r="G203" t="n">
-        <v>245</v>
-      </c>
-      <c r="H203" t="n">
-        <v>149</v>
-      </c>
-      <c r="I203" t="n">
-        <v>42</v>
-      </c>
-      <c r="J203" t="n">
-        <v>27</v>
-      </c>
-      <c r="K203" t="n">
-        <v>77</v>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12979,26 +13035,40 @@
           <t>.759</t>
         </is>
       </c>
-      <c r="E204" t="n">
-        <v>49</v>
-      </c>
-      <c r="F204" t="n">
-        <v>588</v>
-      </c>
-      <c r="G204" t="n">
-        <v>237</v>
-      </c>
-      <c r="H204" t="n">
-        <v>167</v>
-      </c>
-      <c r="I204" t="n">
-        <v>38</v>
-      </c>
-      <c r="J204" t="n">
-        <v>38</v>
-      </c>
-      <c r="K204" t="n">
-        <v>80</v>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -13027,26 +13097,40 @@
           <t>.850</t>
         </is>
       </c>
-      <c r="E205" t="n">
-        <v>65</v>
-      </c>
-      <c r="F205" t="n">
-        <v>692</v>
-      </c>
-      <c r="G205" t="n">
-        <v>192</v>
-      </c>
-      <c r="H205" t="n">
-        <v>154</v>
-      </c>
-      <c r="I205" t="n">
-        <v>26</v>
-      </c>
-      <c r="J205" t="n">
-        <v>19</v>
-      </c>
-      <c r="K205" t="n">
-        <v>75</v>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -13075,26 +13159,40 @@
           <t>.793</t>
         </is>
       </c>
-      <c r="E206" t="n">
-        <v>120</v>
-      </c>
-      <c r="F206" t="n">
-        <v>841</v>
-      </c>
-      <c r="G206" t="n">
-        <v>218</v>
-      </c>
-      <c r="H206" t="n">
-        <v>190</v>
-      </c>
-      <c r="I206" t="n">
-        <v>57</v>
-      </c>
-      <c r="J206" t="n">
-        <v>19</v>
-      </c>
-      <c r="K206" t="n">
-        <v>78</v>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -13123,30 +13221,428 @@
           <t>.814</t>
         </is>
       </c>
-      <c r="E207" t="n">
-        <v>70</v>
-      </c>
-      <c r="F207" t="n">
-        <v>770</v>
-      </c>
-      <c r="G207" t="n">
-        <v>253</v>
-      </c>
-      <c r="H207" t="n">
-        <v>215</v>
-      </c>
-      <c r="I207" t="n">
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>50/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Ducksnation</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>.565</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>.941</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>12</v>
+      </c>
+      <c r="F208" t="n">
+        <v>132</v>
+      </c>
+      <c r="G208" t="n">
+        <v>47</v>
+      </c>
+      <c r="H208" t="n">
+        <v>32</v>
+      </c>
+      <c r="I208" t="n">
+        <v>5</v>
+      </c>
+      <c r="J208" t="n">
+        <v>8</v>
+      </c>
+      <c r="K208" t="n">
+        <v>13</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>7/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Goat Club</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>.514</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>.818</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>12</v>
+      </c>
+      <c r="F209" t="n">
+        <v>104</v>
+      </c>
+      <c r="G209" t="n">
+        <v>36</v>
+      </c>
+      <c r="H209" t="n">
+        <v>29</v>
+      </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>4</v>
+      </c>
+      <c r="K209" t="n">
+        <v>18</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>5/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>VJ's Generators ⚡️</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>.476</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>.824</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>13</v>
+      </c>
+      <c r="F210" t="n">
+        <v>105</v>
+      </c>
+      <c r="G210" t="n">
+        <v>19</v>
+      </c>
+      <c r="H210" t="n">
+        <v>15</v>
+      </c>
+      <c r="I210" t="n">
+        <v>7</v>
+      </c>
+      <c r="J210" t="n">
+        <v>4</v>
+      </c>
+      <c r="K210" t="n">
+        <v>7</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>YOU ARE MY BRONSHINE</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>.598</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>.758</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>12</v>
+      </c>
+      <c r="F211" t="n">
+        <v>159</v>
+      </c>
+      <c r="G211" t="n">
+        <v>59</v>
+      </c>
+      <c r="H211" t="n">
+        <v>30</v>
+      </c>
+      <c r="I211" t="n">
+        <v>8</v>
+      </c>
+      <c r="J211" t="n">
+        <v>13</v>
+      </c>
+      <c r="K211" t="n">
+        <v>15</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>7/34</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Flagg on the Play</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>.585</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>.795</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>12</v>
+      </c>
+      <c r="F212" t="n">
+        <v>167</v>
+      </c>
+      <c r="G212" t="n">
+        <v>35</v>
+      </c>
+      <c r="H212" t="n">
+        <v>29</v>
+      </c>
+      <c r="I212" t="n">
+        <v>5</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>14</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>7/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Thomas's Team</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>.432</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>.893</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>13</v>
+      </c>
+      <c r="F213" t="n">
+        <v>120</v>
+      </c>
+      <c r="G213" t="n">
+        <v>28</v>
+      </c>
+      <c r="H213" t="n">
+        <v>31</v>
+      </c>
+      <c r="I213" t="n">
+        <v>8</v>
+      </c>
+      <c r="J213" t="n">
+        <v>5</v>
+      </c>
+      <c r="K213" t="n">
+        <v>11</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Jerome (Ty)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>.308</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>.909</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>36</v>
+      </c>
+      <c r="G214" t="n">
+        <v>27</v>
+      </c>
+      <c r="H214" t="n">
+        <v>23</v>
+      </c>
+      <c r="I214" t="n">
+        <v>7</v>
+      </c>
+      <c r="J214" t="n">
+        <v>6</v>
+      </c>
+      <c r="K214" t="n">
+        <v>9</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Fab's Fascinating Team</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>.459</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>.909</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>6</v>
+      </c>
+      <c r="F215" t="n">
         <v>50</v>
       </c>
-      <c r="J207" t="n">
-        <v>19</v>
-      </c>
-      <c r="K207" t="n">
-        <v>101</v>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>50/50</t>
+      <c r="G215" t="n">
+        <v>6</v>
+      </c>
+      <c r="H215" t="n">
+        <v>10</v>
+      </c>
+      <c r="I215" t="n">
+        <v>4</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="n">
+        <v>5</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>4/44</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.565</t>
+          <t>.562</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.941</t>
+          <t>.950</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F208" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G208" t="n">
         <v>47</v>
       </c>
       <c r="H208" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
         <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>7/40</t>
+          <t>9/42</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.514</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.818</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F209" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="G209" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H209" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J209" t="n">
         <v>4</v>
       </c>
       <c r="K209" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>5/43</t>
+          <t>8/46</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.476</t>
+          <t>.448</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.824</t>
+          <t>.875</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>13</v>
       </c>
       <c r="F210" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G210" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H210" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I210" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J210" t="n">
         <v>4</v>
       </c>
       <c r="K210" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -13419,25 +13419,25 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.598</t>
+          <t>.606</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.758</t>
+          <t>.714</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>12</v>
       </c>
       <c r="F211" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G211" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H211" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I211" t="n">
         <v>8</v>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>7/34</t>
+          <t>8/35</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.585</t>
+          <t>.569</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.795</t>
+          <t>.791</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F212" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G212" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H212" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I212" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J212" t="n">
         <v>1</v>
       </c>
       <c r="K212" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>7/43</t>
+          <t>10/43</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.432</t>
+          <t>.431</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13524,19 +13524,19 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F213" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G213" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H213" t="n">
         <v>31</v>
       </c>
       <c r="I213" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J213" t="n">
         <v>5</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/32</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.308</t>
+          <t>.403</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.909</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F214" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="G214" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H214" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J214" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K214" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>8/37</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>4/44</t>
+          <t>5/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13498,7 +13498,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>10/43</t>
+          <t>10/46</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>7/32</t>
+          <t>7/35</t>
         </is>
       </c>
     </row>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>8/37</t>
+          <t>8/40</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>5/45</t>
+          <t>5/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.562</t>
+          <t>.549</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.950</t>
+          <t>.976</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F208" t="n">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="G208" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="H208" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I208" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J208" t="n">
         <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>9/42</t>
+          <t>12/42</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.784</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F209" t="n">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="G209" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="H209" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J209" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K209" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>8/46</t>
+          <t>13/49</t>
         </is>
       </c>
     </row>
@@ -13371,25 +13371,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.448</t>
+          <t>.433</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.875</t>
+          <t>.815</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>13</v>
       </c>
       <c r="F210" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G210" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H210" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I210" t="n">
         <v>8</v>
@@ -13398,11 +13398,11 @@
         <v>4</v>
       </c>
       <c r="K210" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.606</t>
+          <t>.580</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.714</t>
+          <t>.722</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>12</v>
       </c>
       <c r="F211" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G211" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H211" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I211" t="n">
         <v>8</v>
       </c>
       <c r="J211" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K211" t="n">
         <v>15</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>8/35</t>
+          <t>9/35</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.569</t>
+          <t>.596</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.791</t>
+          <t>.815</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F212" t="n">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="G212" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H212" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K212" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>10/46</t>
+          <t>14/47</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.431</t>
+          <t>.415</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13524,29 +13524,29 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F213" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="G213" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H213" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>7/35</t>
+          <t>9/39</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.403</t>
+          <t>.396</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.829</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F214" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G214" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="H214" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="I214" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J214" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K214" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>8/40</t>
+          <t>11/46</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.459</t>
+          <t>.452</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.909</t>
+          <t>.878</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F215" t="n">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="G215" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H215" t="n">
+        <v>42</v>
+      </c>
+      <c r="I215" t="n">
         <v>10</v>
       </c>
-      <c r="I215" t="n">
+      <c r="J215" t="n">
         <v>4</v>
       </c>
-      <c r="J215" t="n">
-        <v>3</v>
-      </c>
       <c r="K215" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>5/48</t>
+          <t>12/46</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.433</t>
+          <t>.438</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13380,19 +13380,19 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F210" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="G210" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H210" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I210" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J210" t="n">
         <v>4</v>
@@ -13467,28 +13467,28 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.596</t>
+          <t>.595</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.815</t>
+          <t>.821</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F212" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G212" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H212" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J212" t="n">
         <v>3</v>
@@ -13515,25 +13515,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.415</t>
+          <t>.421</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.893</t>
+          <t>.861</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F213" t="n">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="G213" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H213" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I213" t="n">
         <v>11</v>
@@ -13542,7 +13542,7 @@
         <v>6</v>
       </c>
       <c r="K213" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -13563,34 +13563,34 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.396</t>
+          <t>.383</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.829</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G214" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H214" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I214" t="n">
         <v>14</v>
       </c>
       <c r="J214" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K214" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -13611,25 +13611,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.452</t>
+          <t>.470</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.878</t>
+          <t>.870</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F215" t="n">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G215" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="H215" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I215" t="n">
         <v>10</v>
@@ -13638,7 +13638,7 @@
         <v>4</v>
       </c>
       <c r="K215" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.438</t>
+          <t>.431</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13383,13 +13383,13 @@
         <v>18</v>
       </c>
       <c r="F210" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G210" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H210" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I210" t="n">
         <v>9</v>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -13467,22 +13467,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.595</t>
+          <t>.591</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.821</t>
+          <t>.826</t>
         </is>
       </c>
       <c r="E212" t="n">
         <v>24</v>
       </c>
       <c r="F212" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G212" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H212" t="n">
         <v>48</v>
@@ -13491,14 +13491,14 @@
         <v>9</v>
       </c>
       <c r="J212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K212" t="n">
         <v>28</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>14/47</t>
+          <t>15/48</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.421</t>
+          <t>.423</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13527,10 +13527,10 @@
         <v>26</v>
       </c>
       <c r="F213" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G213" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H213" t="n">
         <v>50</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>9/39</t>
+          <t>10/40</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.383</t>
+          <t>.393</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13572,16 +13572,16 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F214" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G214" t="n">
         <v>62</v>
       </c>
       <c r="H214" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I214" t="n">
         <v>14</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>11/46</t>
+          <t>12/47</t>
         </is>
       </c>
     </row>
@@ -13611,25 +13611,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.470</t>
+          <t>.468</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.870</t>
+          <t>.854</t>
         </is>
       </c>
       <c r="E215" t="n">
         <v>22</v>
       </c>
       <c r="F215" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="G215" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H215" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I215" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>12/46</t>
+          <t>14/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.549</t>
+          <t>.525</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.976</t>
+          <t>.931</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F208" t="n">
-        <v>217</v>
+        <v>375</v>
       </c>
       <c r="G208" t="n">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="H208" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="I208" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J208" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K208" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>12/42</t>
+          <t>20/41</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.497</t>
+          <t>.493</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.784</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F209" t="n">
-        <v>198</v>
+        <v>302</v>
       </c>
       <c r="G209" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="H209" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="I209" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J209" t="n">
         <v>6</v>
       </c>
       <c r="K209" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>13/49</t>
+          <t>17/42</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.431</t>
+          <t>.473</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.815</t>
+          <t>.792</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F210" t="n">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="G210" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="H210" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I210" t="n">
+        <v>12</v>
+      </c>
+      <c r="J210" t="n">
         <v>9</v>
       </c>
-      <c r="J210" t="n">
-        <v>4</v>
-      </c>
       <c r="K210" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.580</t>
+          <t>.560</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.722</t>
+          <t>.700</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F211" t="n">
-        <v>168</v>
+        <v>286</v>
       </c>
       <c r="G211" t="n">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="H211" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I211" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J211" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K211" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>9/35</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.591</t>
+          <t>.553</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.826</t>
+          <t>.798</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F212" t="n">
-        <v>275</v>
+        <v>373</v>
       </c>
       <c r="G212" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="H212" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="I212" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J212" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K212" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>15/48</t>
+          <t>21/41</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.423</t>
+          <t>.404</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.861</t>
+          <t>.846</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F213" t="n">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G213" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="H213" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="I213" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J213" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K213" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>10/40</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.393</t>
+          <t>.444</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.869</t>
         </is>
       </c>
       <c r="E214" t="n">
+        <v>31</v>
+      </c>
+      <c r="F214" t="n">
+        <v>286</v>
+      </c>
+      <c r="G214" t="n">
+        <v>102</v>
+      </c>
+      <c r="H214" t="n">
+        <v>105</v>
+      </c>
+      <c r="I214" t="n">
+        <v>22</v>
+      </c>
+      <c r="J214" t="n">
         <v>16</v>
       </c>
-      <c r="F214" t="n">
-        <v>145</v>
-      </c>
-      <c r="G214" t="n">
-        <v>62</v>
-      </c>
-      <c r="H214" t="n">
-        <v>57</v>
-      </c>
-      <c r="I214" t="n">
-        <v>14</v>
-      </c>
-      <c r="J214" t="n">
-        <v>12</v>
-      </c>
       <c r="K214" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>12/47</t>
+          <t>18/41</t>
         </is>
       </c>
     </row>
@@ -13616,33 +13616,33 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.854</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F215" t="n">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="G215" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="H215" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="I215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J215" t="n">
         <v>4</v>
       </c>
       <c r="K215" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>14/48</t>
+          <t>18/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.525</t>
+          <t>.529</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.931</t>
+          <t>.932</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F208" t="n">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="G208" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H208" t="n">
         <v>74</v>
       </c>
       <c r="I208" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J208" t="n">
         <v>12</v>
       </c>
       <c r="K208" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>20/41</t>
+          <t>22/43</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.493</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.841</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F209" t="n">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="G209" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H209" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J209" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K209" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>17/42</t>
+          <t>21/46</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.473</t>
+          <t>.471</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.792</t>
+          <t>.808</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F210" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G210" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H210" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I210" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J210" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K210" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.560</t>
+          <t>.551</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.700</t>
+          <t>.719</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>20</v>
       </c>
       <c r="F211" t="n">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="G211" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H211" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I211" t="n">
         <v>15</v>
       </c>
       <c r="J211" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K211" t="n">
         <v>37</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/34</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.553</t>
+          <t>.552</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.798</t>
+          <t>.792</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F212" t="n">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="G212" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H212" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I212" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K212" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>21/41</t>
+          <t>25/45</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.404</t>
+          <t>.408</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.846</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F213" t="n">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="G213" t="n">
+        <v>104</v>
+      </c>
+      <c r="H213" t="n">
         <v>84</v>
       </c>
-      <c r="H213" t="n">
-        <v>73</v>
-      </c>
       <c r="I213" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K213" t="n">
         <v>29</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/34</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.444</t>
+          <t>.462</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.869</t>
+          <t>.875</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F214" t="n">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="G214" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H214" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I214" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J214" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K214" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>18/41</t>
+          <t>22/45</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.468</t>
+          <t>.472</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.859</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F215" t="n">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="G215" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H215" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I215" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J215" t="n">
         <v>4</v>
       </c>
       <c r="K215" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>18/45</t>
+          <t>21/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>20/34</t>
+          <t>20/35</t>
         </is>
       </c>
     </row>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>22/45</t>
+          <t>22/47</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,25 +13275,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.529</t>
+          <t>.534</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.932</t>
+          <t>.931</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F208" t="n">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="G208" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H208" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I208" t="n">
         <v>20</v>
@@ -13302,11 +13302,11 @@
         <v>12</v>
       </c>
       <c r="K208" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>22/43</t>
+          <t>24/45</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.508</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.841</t>
+          <t>.812</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F209" t="n">
-        <v>321</v>
+        <v>436</v>
       </c>
       <c r="G209" t="n">
+        <v>153</v>
+      </c>
+      <c r="H209" t="n">
         <v>112</v>
       </c>
-      <c r="H209" t="n">
-        <v>83</v>
-      </c>
       <c r="I209" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J209" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K209" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>21/46</t>
+          <t>28/50</t>
         </is>
       </c>
     </row>
@@ -13371,25 +13371,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.471</t>
+          <t>.475</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.808</t>
+          <t>.823</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>30</v>
       </c>
       <c r="F210" t="n">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="G210" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H210" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I210" t="n">
         <v>13</v>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.551</t>
+          <t>.542</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.719</t>
+          <t>.701</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>20</v>
       </c>
       <c r="F211" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G211" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H211" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I211" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J211" t="n">
         <v>30</v>
       </c>
       <c r="K211" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>18/34</t>
+          <t>19/34</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.552</t>
+          <t>.538</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.792</t>
+          <t>.809</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F212" t="n">
-        <v>387</v>
+        <v>461</v>
       </c>
       <c r="G212" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H212" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I212" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J212" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K212" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>25/45</t>
+          <t>29/46</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.408</t>
+          <t>.419</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.864</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F213" t="n">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="G213" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H213" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I213" t="n">
         <v>20</v>
       </c>
       <c r="J213" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K213" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>20/35</t>
+          <t>23/45</t>
         </is>
       </c>
     </row>
@@ -13572,29 +13572,29 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F214" t="n">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="G214" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H214" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I214" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J214" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K214" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>22/47</t>
+          <t>24/47</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.472</t>
+          <t>.471</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.859</t>
+          <t>.856</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F215" t="n">
-        <v>335</v>
+        <v>433</v>
       </c>
       <c r="G215" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="H215" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="I215" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K215" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>21/48</t>
+          <t>28/49</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.534</t>
+          <t>.487</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.931</t>
+          <t>.894</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F208" t="n">
-        <v>425</v>
+        <v>554</v>
       </c>
       <c r="G208" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="H208" t="n">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="I208" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J208" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K208" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>24/45</t>
+          <t>33/43</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.508</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.812</t>
+          <t>.796</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F209" t="n">
-        <v>436</v>
+        <v>510</v>
       </c>
       <c r="G209" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="H209" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="I209" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J209" t="n">
         <v>9</v>
       </c>
       <c r="K209" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>28/50</t>
+          <t>30/46</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.475</t>
+          <t>.472</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.823</t>
+          <t>.781</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F210" t="n">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="G210" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H210" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I210" t="n">
+        <v>17</v>
+      </c>
+      <c r="J210" t="n">
         <v>13</v>
       </c>
-      <c r="J210" t="n">
-        <v>11</v>
-      </c>
       <c r="K210" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.542</t>
+          <t>.523</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.701</t>
+          <t>.711</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F211" t="n">
-        <v>325</v>
+        <v>405</v>
       </c>
       <c r="G211" t="n">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="H211" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="I211" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J211" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K211" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>19/34</t>
+          <t>25/34</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.538</t>
+          <t>.540</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.809</t>
+          <t>.800</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F212" t="n">
-        <v>461</v>
+        <v>548</v>
       </c>
       <c r="G212" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="H212" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I212" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J212" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K212" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>29/46</t>
+          <t>34/44</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.419</t>
+          <t>.422</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.864</t>
+          <t>.859</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F213" t="n">
-        <v>352</v>
+        <v>487</v>
       </c>
       <c r="G213" t="n">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="H213" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="I213" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J213" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K213" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>23/45</t>
+          <t>29/41</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.462</t>
+          <t>.456</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.875</t>
+          <t>.857</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F214" t="n">
-        <v>358</v>
+        <v>503</v>
       </c>
       <c r="G214" t="n">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="H214" t="n">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="I214" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J214" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K214" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>24/47</t>
+          <t>28/41</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.471</t>
+          <t>.490</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.856</t>
+          <t>.864</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F215" t="n">
-        <v>433</v>
+        <v>553</v>
       </c>
       <c r="G215" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="H215" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="I215" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J215" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K215" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>28/49</t>
+          <t>33/46</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13306,7 +13306,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>33/43</t>
+          <t>34/44</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.499</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.796</t>
+          <t>.793</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F209" t="n">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="G209" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H209" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I209" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J209" t="n">
         <v>9</v>
       </c>
       <c r="K209" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>30/46</t>
+          <t>34/50</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.472</t>
+          <t>.475</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.781</t>
+          <t>.773</t>
         </is>
       </c>
       <c r="E210" t="n">
         <v>35</v>
       </c>
       <c r="F210" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="G210" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H210" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I210" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J210" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K210" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>25/34</t>
+          <t>26/35</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.540</t>
+          <t>.539</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.800</t>
+          <t>.798</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F212" t="n">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="G212" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H212" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I212" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J212" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K212" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>34/44</t>
+          <t>37/47</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.422</t>
+          <t>.426</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.859</t>
+          <t>.869</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F213" t="n">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="G213" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H213" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I213" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J213" t="n">
         <v>21</v>
       </c>
       <c r="K213" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>29/41</t>
+          <t>33/45</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.456</t>
+          <t>.458</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.857</t>
+          <t>.854</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F214" t="n">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="G214" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H214" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I214" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J214" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K214" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>28/41</t>
+          <t>34/47</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.490</t>
+          <t>.494</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.864</t>
+          <t>.837</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F215" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="G215" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H215" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I215" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J215" t="n">
         <v>10</v>
       </c>
       <c r="K215" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>33/46</t>
+          <t>36/49</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.487</t>
+          <t>.491</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.894</t>
+          <t>.895</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F208" t="n">
-        <v>554</v>
+        <v>604</v>
       </c>
       <c r="G208" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H208" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I208" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J208" t="n">
         <v>16</v>
       </c>
       <c r="K208" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>34/44</t>
+          <t>36/44</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.499</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.793</t>
+          <t>.795</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F209" t="n">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="G209" t="n">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="H209" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="I209" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J209" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K209" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>34/50</t>
+          <t>40/50</t>
         </is>
       </c>
     </row>
@@ -13371,38 +13371,38 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.475</t>
+          <t>.480</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.773</t>
+          <t>.765</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F210" t="n">
-        <v>321</v>
+        <v>399</v>
       </c>
       <c r="G210" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="H210" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I210" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J210" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.523</t>
+          <t>.503</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.711</t>
+          <t>.755</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F211" t="n">
-        <v>405</v>
+        <v>490</v>
       </c>
       <c r="G211" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="H211" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="I211" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J211" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K211" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>26/35</t>
+          <t>31/35</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.539</t>
+          <t>.520</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.798</t>
+          <t>.794</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F212" t="n">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="G212" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H212" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I212" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J212" t="n">
         <v>12</v>
       </c>
       <c r="K212" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>41/47</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.426</t>
+          <t>.428</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.869</t>
+          <t>.863</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F213" t="n">
-        <v>516</v>
+        <v>586</v>
       </c>
       <c r="G213" t="n">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="H213" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I213" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J213" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K213" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>33/45</t>
+          <t>35/42</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.458</t>
+          <t>.463</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.854</t>
+          <t>.859</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F214" t="n">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="G214" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="H214" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="I214" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J214" t="n">
         <v>22</v>
       </c>
       <c r="K214" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>34/47</t>
+          <t>36/46</t>
         </is>
       </c>
     </row>
@@ -13611,38 +13611,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.494</t>
+          <t>.499</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.837</t>
+          <t>.819</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F215" t="n">
-        <v>577</v>
+        <v>650</v>
       </c>
       <c r="G215" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="H215" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="I215" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J215" t="n">
         <v>10</v>
       </c>
       <c r="K215" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>36/49</t>
+          <t>40/50</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,25 +13275,25 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.491</t>
+          <t>.489</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.895</t>
+          <t>.896</t>
         </is>
       </c>
       <c r="E208" t="n">
         <v>62</v>
       </c>
       <c r="F208" t="n">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G208" t="n">
         <v>184</v>
       </c>
       <c r="H208" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I208" t="n">
         <v>36</v>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>36/44</t>
+          <t>37/45</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>.480</t>
+          <t>.477</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13380,19 +13380,19 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F210" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G210" t="n">
         <v>125</v>
       </c>
       <c r="H210" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I210" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J210" t="n">
         <v>17</v>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/32</t>
         </is>
       </c>
     </row>
@@ -13515,25 +13515,25 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.428</t>
+          <t>.425</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.863</t>
+          <t>.856</t>
         </is>
       </c>
       <c r="E213" t="n">
         <v>78</v>
       </c>
       <c r="F213" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G213" t="n">
         <v>207</v>
       </c>
       <c r="H213" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I213" t="n">
         <v>36</v>
@@ -13542,11 +13542,11 @@
         <v>25</v>
       </c>
       <c r="K213" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>35/42</t>
+          <t>38/45</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.463</t>
+          <t>.464</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13575,7 +13575,7 @@
         <v>64</v>
       </c>
       <c r="F214" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G214" t="n">
         <v>204</v>
@@ -13590,11 +13590,11 @@
         <v>22</v>
       </c>
       <c r="K214" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>36/46</t>
+          <t>37/47</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,38 +13275,38 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.489</t>
+          <t>.496</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>.896</t>
+          <t>.878</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F208" t="n">
-        <v>607</v>
+        <v>760</v>
       </c>
       <c r="G208" t="n">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="H208" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="I208" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J208" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K208" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>37/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -13323,38 +13323,38 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.483</t>
+          <t>.481</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.795</t>
+          <t>.809</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F209" t="n">
-        <v>629</v>
+        <v>776</v>
       </c>
       <c r="G209" t="n">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="H209" t="n">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="I209" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J209" t="n">
         <v>12</v>
       </c>
       <c r="K209" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>40/50</t>
+          <t>49/49</t>
         </is>
       </c>
     </row>
@@ -13376,33 +13376,33 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.765</t>
+          <t>.740</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F210" t="n">
-        <v>404</v>
+        <v>459</v>
       </c>
       <c r="G210" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="H210" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I210" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J210" t="n">
         <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>27/32</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -13419,38 +13419,38 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>.503</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.755</t>
+          <t>.750</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F211" t="n">
-        <v>490</v>
+        <v>558</v>
       </c>
       <c r="G211" t="n">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="H211" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I211" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J211" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K211" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>31/35</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -13467,38 +13467,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>.520</t>
+          <t>.507</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>.794</t>
+          <t>.807</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F212" t="n">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="G212" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="H212" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I212" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J212" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K212" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>41/47</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -13515,38 +13515,38 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>.425</t>
+          <t>.431</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>.856</t>
+          <t>.845</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F213" t="n">
-        <v>589</v>
+        <v>699</v>
       </c>
       <c r="G213" t="n">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="H213" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="I213" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J213" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K213" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>38/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.464</t>
+          <t>.455</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.859</t>
+          <t>.861</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F214" t="n">
-        <v>576</v>
+        <v>666</v>
       </c>
       <c r="G214" t="n">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="H214" t="n">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="I214" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J214" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K214" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>37/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -13616,33 +13616,33 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.819</t>
+          <t>.807</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="F215" t="n">
-        <v>650</v>
+        <v>803</v>
       </c>
       <c r="G215" t="n">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="H215" t="n">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="I215" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K215" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>40/50</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>.496</t>
+          <t>.497</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13284,16 +13284,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F208" t="n">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="G208" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H208" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I208" t="n">
         <v>40</v>
@@ -13302,11 +13302,11 @@
         <v>18</v>
       </c>
       <c r="K208" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -13323,19 +13323,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>.481</t>
+          <t>.479</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>.809</t>
+          <t>.812</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F209" t="n">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="G209" t="n">
         <v>268</v>
@@ -13350,11 +13350,11 @@
         <v>12</v>
       </c>
       <c r="K209" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>49/49</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -13563,38 +13563,38 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>.455</t>
+          <t>.459</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>.861</t>
+          <t>.862</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F214" t="n">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="G214" t="n">
         <v>239</v>
       </c>
       <c r="H214" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I214" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J214" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K214" t="n">
         <v>84</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -13611,25 +13611,25 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>.499</t>
+          <t>.501</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>.807</t>
+          <t>.810</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F215" t="n">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="G215" t="n">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="H215" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I215" t="n">
         <v>48</v>
@@ -13638,11 +13638,11 @@
         <v>15</v>
       </c>
       <c r="K215" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -13283,26 +13283,40 @@
           <t>.878</t>
         </is>
       </c>
-      <c r="E208" t="n">
-        <v>73</v>
-      </c>
-      <c r="F208" t="n">
-        <v>767</v>
-      </c>
-      <c r="G208" t="n">
-        <v>238</v>
-      </c>
-      <c r="H208" t="n">
-        <v>152</v>
-      </c>
-      <c r="I208" t="n">
-        <v>40</v>
-      </c>
-      <c r="J208" t="n">
-        <v>18</v>
-      </c>
-      <c r="K208" t="n">
-        <v>72</v>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -13331,26 +13345,40 @@
           <t>.812</t>
         </is>
       </c>
-      <c r="E209" t="n">
-        <v>100</v>
-      </c>
-      <c r="F209" t="n">
-        <v>781</v>
-      </c>
-      <c r="G209" t="n">
-        <v>268</v>
-      </c>
-      <c r="H209" t="n">
-        <v>184</v>
-      </c>
-      <c r="I209" t="n">
-        <v>30</v>
-      </c>
-      <c r="J209" t="n">
-        <v>12</v>
-      </c>
-      <c r="K209" t="n">
-        <v>85</v>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -13379,26 +13407,40 @@
           <t>.740</t>
         </is>
       </c>
-      <c r="E210" t="n">
-        <v>51</v>
-      </c>
-      <c r="F210" t="n">
-        <v>459</v>
-      </c>
-      <c r="G210" t="n">
-        <v>144</v>
-      </c>
-      <c r="H210" t="n">
-        <v>86</v>
-      </c>
-      <c r="I210" t="n">
-        <v>25</v>
-      </c>
-      <c r="J210" t="n">
-        <v>17</v>
-      </c>
-      <c r="K210" t="n">
-        <v>49</v>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -13427,26 +13469,40 @@
           <t>.750</t>
         </is>
       </c>
-      <c r="E211" t="n">
-        <v>36</v>
-      </c>
-      <c r="F211" t="n">
-        <v>558</v>
-      </c>
-      <c r="G211" t="n">
-        <v>265</v>
-      </c>
-      <c r="H211" t="n">
-        <v>132</v>
-      </c>
-      <c r="I211" t="n">
-        <v>33</v>
-      </c>
-      <c r="J211" t="n">
-        <v>45</v>
-      </c>
-      <c r="K211" t="n">
-        <v>63</v>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -13475,26 +13531,40 @@
           <t>.807</t>
         </is>
       </c>
-      <c r="E212" t="n">
-        <v>61</v>
-      </c>
-      <c r="F212" t="n">
-        <v>658</v>
-      </c>
-      <c r="G212" t="n">
-        <v>194</v>
-      </c>
-      <c r="H212" t="n">
-        <v>141</v>
-      </c>
-      <c r="I212" t="n">
-        <v>31</v>
-      </c>
-      <c r="J212" t="n">
-        <v>14</v>
-      </c>
-      <c r="K212" t="n">
-        <v>83</v>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -13523,26 +13593,40 @@
           <t>.845</t>
         </is>
       </c>
-      <c r="E213" t="n">
-        <v>91</v>
-      </c>
-      <c r="F213" t="n">
-        <v>699</v>
-      </c>
-      <c r="G213" t="n">
-        <v>242</v>
-      </c>
-      <c r="H213" t="n">
-        <v>172</v>
-      </c>
-      <c r="I213" t="n">
-        <v>44</v>
-      </c>
-      <c r="J213" t="n">
-        <v>27</v>
-      </c>
-      <c r="K213" t="n">
-        <v>73</v>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -13571,26 +13655,40 @@
           <t>.862</t>
         </is>
       </c>
-      <c r="E214" t="n">
-        <v>74</v>
-      </c>
-      <c r="F214" t="n">
-        <v>677</v>
-      </c>
-      <c r="G214" t="n">
-        <v>239</v>
-      </c>
-      <c r="H214" t="n">
-        <v>224</v>
-      </c>
-      <c r="I214" t="n">
-        <v>42</v>
-      </c>
-      <c r="J214" t="n">
-        <v>30</v>
-      </c>
-      <c r="K214" t="n">
-        <v>84</v>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -13619,26 +13717,40 @@
           <t>.810</t>
         </is>
       </c>
-      <c r="E215" t="n">
-        <v>94</v>
-      </c>
-      <c r="F215" t="n">
-        <v>820</v>
-      </c>
-      <c r="G215" t="n">
-        <v>263</v>
-      </c>
-      <c r="H215" t="n">
-        <v>218</v>
-      </c>
-      <c r="I215" t="n">
-        <v>48</v>
-      </c>
-      <c r="J215" t="n">
-        <v>15</v>
-      </c>
-      <c r="K215" t="n">
-        <v>77</v>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>

--- a/output.xlsx
+++ b/output.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>50/50</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>25/25</t>
+          <t>23/23</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>21/21</t>
+          <t>20/20</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>29/29</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>30/30</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>34/34</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>49/49</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>56/56</t>
+          <t>55/55</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>49/49</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>50/50</t>
+          <t>49/49</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>34/34</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>21/21</t>
+          <t>22/22</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>23/23</t>
+          <t>22/22</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>34/34</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>55/55</t>
+          <t>54/54</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>49/49</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>49/49</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -10592,7 +10592,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>56/56</t>
+          <t>53/53</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>23/23</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>19/19</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>21/21</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>49/49</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>53/53</t>
+          <t>52/52</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>54/54</t>
+          <t>53/53</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>19/19</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>51/51</t>
+          <t>50/50</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>50/50</t>
+          <t>49/49</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>54/54</t>
+          <t>52/52</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>30/30</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23/23</t>
+          <t>24/24</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>33/33</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>25/25</t>
+          <t>24/24</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>21/21</t>
+          <t>23/23</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>28/28</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>19/19</t>
+          <t>20/20</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>46/46</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>36/36</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>48/48</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>47/47</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>53/53</t>
+          <t>51/51</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>52/52</t>
+          <t>53/53</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>55/55</t>
+          <t>56/56</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>32/32</t>
+          <t>33/33</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>36/36</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>41/41</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>43/43</t>
+          <t>42/42</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>35/35</t>
+          <t>34/34</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>47/47</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>37/37</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>46/46</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>31/31</t>
+          <t>32/32</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>57/57</t>
+          <t>54/54</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40/40</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -11212,7 +11212,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -12328,7 +12328,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>38/38</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>41/41</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>39/39</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>42/42</t>
+          <t>44/44</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>53/53</t>
+          <t>55/55</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>39/39</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>38/38</t>
+          <t>45/45</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>45/45</t>
+          <t>48/48</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>40/40</t>
         </is>
       </c>
     </row>

--- a/output.xlsx
+++ b/output.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30/30</t>
+          <t>29/29</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44/44</t>
+          <t>43/43</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>37/37</t>
+          <t>35/35</t>
         </is>
       </c>
     </row>
